--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ КИ/Копия дв 250626 лгрсч пок ки от Воронкова.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ КИ/Копия дв 250626 лгрсч пок ки от Воронкова.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7CA4DB-B4DB-43FF-849C-42A51199B134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A999DEF-81AD-4BD4-BACB-80CB51FF9A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -903,7 +903,7 @@
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
     <numFmt numFmtId="165" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -937,6 +937,30 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -1018,7 +1042,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1037,9 +1061,14 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -5314,7 +5343,9 @@
     <col min="15" max="15" width="11.42578125" customWidth="1"/>
     <col min="16" max="16" width="6" customWidth="1"/>
     <col min="17" max="17" width="6.85546875" customWidth="1"/>
-    <col min="18" max="22" width="7" customWidth="1"/>
+    <col min="18" max="20" width="7" customWidth="1"/>
+    <col min="21" max="21" width="7" style="25" customWidth="1"/>
+    <col min="22" max="22" width="7" customWidth="1"/>
     <col min="23" max="23" width="21" customWidth="1"/>
     <col min="24" max="25" width="5" customWidth="1"/>
     <col min="26" max="29" width="6.85546875" customWidth="1"/>
@@ -5345,7 +5376,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="18">
+      <c r="U1" s="19">
         <v>1.1499999999999999</v>
       </c>
       <c r="V1" s="1"/>
@@ -5402,7 +5433,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+      <c r="U2" s="20"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -5497,7 +5528,7 @@
       <c r="T3" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="21" t="s">
         <v>286</v>
       </c>
       <c r="V3" s="7" t="s">
@@ -5584,7 +5615,7 @@
       </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1" t="s">
+      <c r="U4" s="20" t="s">
         <v>287</v>
       </c>
       <c r="V4" s="1"/>
@@ -5687,7 +5718,7 @@
         <f t="shared" si="1"/>
         <v>16089.24065</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5" s="22">
         <f t="shared" si="1"/>
         <v>23704.320910000006</v>
       </c>
@@ -5798,7 +5829,7 @@
         <f>S6</f>
         <v>0</v>
       </c>
-      <c r="U6" s="5">
+      <c r="U6" s="23">
         <f>T6</f>
         <v>0</v>
       </c>
@@ -5914,7 +5945,7 @@
         <f t="shared" ref="T7:T70" si="5">S7</f>
         <v>185.12194799999952</v>
       </c>
-      <c r="U7" s="5">
+      <c r="U7" s="23">
         <f>T7+R7*$U$1</f>
         <v>454.17548799999952</v>
       </c>
@@ -6025,7 +6056,7 @@
         <f>V8</f>
         <v>300</v>
       </c>
-      <c r="U8" s="5">
+      <c r="U8" s="23">
         <f t="shared" ref="U8:U70" si="9">T8</f>
         <v>300</v>
       </c>
@@ -6143,7 +6174,7 @@
         <f t="shared" si="5"/>
         <v>301.19999999999982</v>
       </c>
-      <c r="U9" s="5">
+      <c r="U9" s="23">
         <f t="shared" ref="U9:U11" si="10">T9+R9*$U$1</f>
         <v>429.53999999999979</v>
       </c>
@@ -6255,7 +6286,7 @@
         <f t="shared" si="5"/>
         <v>203.80000000000018</v>
       </c>
-      <c r="U10" s="5">
+      <c r="U10" s="23">
         <f t="shared" si="10"/>
         <v>442.31000000000017</v>
       </c>
@@ -6369,7 +6400,7 @@
         <f t="shared" si="5"/>
         <v>28</v>
       </c>
-      <c r="U11" s="5">
+      <c r="U11" s="23">
         <f t="shared" si="10"/>
         <v>46.4</v>
       </c>
@@ -6472,7 +6503,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U12" s="5">
+      <c r="U12" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6583,7 +6614,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U13" s="5">
+      <c r="U13" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -6697,7 +6728,7 @@
         <f t="shared" si="5"/>
         <v>23.448000000000093</v>
       </c>
-      <c r="U14" s="5">
+      <c r="U14" s="23">
         <f t="shared" ref="U14:U16" si="12">T14+R14*$U$1</f>
         <v>77.49800000000009</v>
       </c>
@@ -6809,7 +6840,7 @@
         <f t="shared" si="5"/>
         <v>237.57840000000033</v>
       </c>
-      <c r="U15" s="5">
+      <c r="U15" s="23">
         <f t="shared" si="12"/>
         <v>499.42558000000031</v>
       </c>
@@ -6923,7 +6954,7 @@
         <f t="shared" si="5"/>
         <v>369.30099999999766</v>
       </c>
-      <c r="U16" s="5">
+      <c r="U16" s="23">
         <f t="shared" si="12"/>
         <v>1177.7107499999975</v>
       </c>
@@ -7034,7 +7065,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U17" s="5">
+      <c r="U17" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -7145,7 +7176,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U18" s="5">
+      <c r="U18" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -7261,7 +7292,7 @@
         <f t="shared" si="5"/>
         <v>30.240367999999961</v>
       </c>
-      <c r="U19" s="5">
+      <c r="U19" s="23">
         <f>T19+R19*$U$1</f>
         <v>50.138587999999956</v>
       </c>
@@ -7370,7 +7401,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U20" s="5">
+      <c r="U20" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -7484,7 +7515,7 @@
         <f t="shared" si="5"/>
         <v>328.3985880000007</v>
       </c>
-      <c r="U21" s="5">
+      <c r="U21" s="23">
         <f>T21+R21*$U$1</f>
         <v>660.23522800000069</v>
       </c>
@@ -7589,7 +7620,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U22" s="5">
+      <c r="U22" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -7698,7 +7729,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U23" s="5">
+      <c r="U23" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -7810,7 +7841,7 @@
         <f t="shared" si="5"/>
         <v>144.96939999999995</v>
       </c>
-      <c r="U24" s="5">
+      <c r="U24" s="23">
         <f t="shared" ref="U24:U25" si="14">T24+R24*$U$1</f>
         <v>268.17947999999996</v>
       </c>
@@ -7926,7 +7957,7 @@
         <f t="shared" si="5"/>
         <v>199.67120000000034</v>
       </c>
-      <c r="U25" s="5">
+      <c r="U25" s="23">
         <f t="shared" si="14"/>
         <v>353.84733000000034</v>
       </c>
@@ -8039,7 +8070,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U26" s="5">
+      <c r="U26" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8150,7 +8181,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U27" s="5">
+      <c r="U27" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8261,7 +8292,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U28" s="5">
+      <c r="U28" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8373,7 +8404,7 @@
         <f t="shared" si="5"/>
         <v>411.67119999999932</v>
       </c>
-      <c r="U29" s="5">
+      <c r="U29" s="23">
         <f>T29+R29*$U$1</f>
         <v>906.14083999999923</v>
       </c>
@@ -8486,7 +8517,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U30" s="5">
+      <c r="U30" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8598,7 +8629,7 @@
         <f t="shared" si="5"/>
         <v>17.978400000000008</v>
       </c>
-      <c r="U31" s="5">
+      <c r="U31" s="23">
         <f t="shared" ref="U31:U37" si="15">T31+R31*$U$1</f>
         <v>22.10598000000001</v>
       </c>
@@ -8710,7 +8741,7 @@
         <f t="shared" si="5"/>
         <v>4425.8896000000013</v>
       </c>
-      <c r="U32" s="5">
+      <c r="U32" s="23">
         <f t="shared" si="15"/>
         <v>5123.6194400000013</v>
       </c>
@@ -8822,7 +8853,7 @@
         <f t="shared" si="5"/>
         <v>93.61119999999994</v>
       </c>
-      <c r="U33" s="5">
+      <c r="U33" s="23">
         <f t="shared" si="15"/>
         <v>149.48578999999992</v>
       </c>
@@ -8934,7 +8965,7 @@
         <f t="shared" si="5"/>
         <v>1920.4000000000015</v>
       </c>
-      <c r="U34" s="5">
+      <c r="U34" s="23">
         <f t="shared" si="15"/>
         <v>2894.6800000000012</v>
       </c>
@@ -9050,7 +9081,7 @@
         <f t="shared" si="5"/>
         <v>379.30200000000013</v>
       </c>
-      <c r="U35" s="5">
+      <c r="U35" s="23">
         <f t="shared" si="15"/>
         <v>494.76200000000011</v>
       </c>
@@ -9164,7 +9195,7 @@
         <f t="shared" si="5"/>
         <v>511.1279999999997</v>
       </c>
-      <c r="U36" s="5">
+      <c r="U36" s="23">
         <f t="shared" si="15"/>
         <v>768.26799999999969</v>
       </c>
@@ -9276,7 +9307,7 @@
         <f t="shared" si="5"/>
         <v>25.4</v>
       </c>
-      <c r="U37" s="5">
+      <c r="U37" s="23">
         <f t="shared" si="15"/>
         <v>29.769999999999996</v>
       </c>
@@ -9379,7 +9410,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U38" s="5">
+      <c r="U38" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9490,7 +9521,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U39" s="5">
+      <c r="U39" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9599,7 +9630,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U40" s="5">
+      <c r="U40" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9712,7 +9743,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U41" s="5">
+      <c r="U41" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9823,7 +9854,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U42" s="5">
+      <c r="U42" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9935,7 +9966,7 @@
         <f t="shared" si="5"/>
         <v>259.59999999999991</v>
       </c>
-      <c r="U43" s="5">
+      <c r="U43" s="23">
         <f t="shared" ref="U43:U45" si="17">T43+R43*$U$1</f>
         <v>314.56999999999988</v>
       </c>
@@ -10047,7 +10078,7 @@
         <f t="shared" si="5"/>
         <v>260.79999999999995</v>
       </c>
-      <c r="U44" s="5">
+      <c r="U44" s="23">
         <f t="shared" si="17"/>
         <v>311.85999999999996</v>
       </c>
@@ -10161,7 +10192,7 @@
         <f t="shared" si="5"/>
         <v>21.938477999999975</v>
       </c>
-      <c r="U45" s="5">
+      <c r="U45" s="23">
         <f t="shared" si="17"/>
         <v>48.096377999999973</v>
       </c>
@@ -10272,7 +10303,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U46" s="5">
+      <c r="U46" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10388,7 +10419,7 @@
         <f t="shared" si="5"/>
         <v>414.80600000000027</v>
       </c>
-      <c r="U47" s="5">
+      <c r="U47" s="23">
         <f>T47+R47*$U$1</f>
         <v>556.48600000000022</v>
       </c>
@@ -10499,7 +10530,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U48" s="5">
+      <c r="U48" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10615,7 +10646,7 @@
         <f t="shared" si="5"/>
         <v>258.11411799999985</v>
       </c>
-      <c r="U49" s="5">
+      <c r="U49" s="23">
         <f>T49+R49*$U$1</f>
         <v>402.94948799999986</v>
       </c>
@@ -10726,7 +10757,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U50" s="5">
+      <c r="U50" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10837,7 +10868,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U51" s="5">
+      <c r="U51" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10951,7 +10982,7 @@
         <f t="shared" si="5"/>
         <v>432.59999999999991</v>
       </c>
-      <c r="U52" s="5">
+      <c r="U52" s="23">
         <f t="shared" ref="U52:U53" si="18">T52+R52*$U$1</f>
         <v>548.51999999999987</v>
       </c>
@@ -11063,7 +11094,7 @@
         <f t="shared" si="5"/>
         <v>24.399999999999977</v>
       </c>
-      <c r="U53" s="5">
+      <c r="U53" s="23">
         <f t="shared" si="18"/>
         <v>46.479999999999976</v>
       </c>
@@ -11172,7 +11203,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U54" s="5">
+      <c r="U54" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11286,7 +11317,7 @@
         <f t="shared" si="5"/>
         <v>78.308599999999956</v>
       </c>
-      <c r="U55" s="5">
+      <c r="U55" s="23">
         <f>T55+R55*$U$1</f>
         <v>260.80830999999995</v>
       </c>
@@ -11395,7 +11426,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U56" s="5">
+      <c r="U56" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11511,7 +11542,7 @@
         <f t="shared" si="5"/>
         <v>89.720548000000463</v>
       </c>
-      <c r="U57" s="5">
+      <c r="U57" s="23">
         <f t="shared" ref="U57:U58" si="19">T57+R57*$U$1</f>
         <v>279.22789800000044</v>
       </c>
@@ -11623,7 +11654,7 @@
         <f t="shared" si="5"/>
         <v>28.669399999999996</v>
       </c>
-      <c r="U58" s="5">
+      <c r="U58" s="23">
         <f t="shared" si="19"/>
         <v>54.211129999999997</v>
       </c>
@@ -11730,7 +11761,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U59" s="5">
+      <c r="U59" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11846,7 +11877,7 @@
         <f t="shared" si="5"/>
         <v>290.23799999999994</v>
       </c>
-      <c r="U60" s="5">
+      <c r="U60" s="23">
         <f t="shared" ref="U60:U61" si="20">T60+R60*$U$1</f>
         <v>353.25799999999992</v>
       </c>
@@ -11962,7 +11993,7 @@
         <f t="shared" si="5"/>
         <v>43.496433999999994</v>
       </c>
-      <c r="U61" s="5">
+      <c r="U61" s="23">
         <f t="shared" si="20"/>
         <v>55.414573999999995</v>
       </c>
@@ -12069,7 +12100,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U62" s="5">
+      <c r="U62" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -12178,7 +12209,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U63" s="5">
+      <c r="U63" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -12292,7 +12323,7 @@
         <f t="shared" si="5"/>
         <v>403.452</v>
       </c>
-      <c r="U64" s="5">
+      <c r="U64" s="23">
         <f t="shared" ref="U64:U65" si="21">T64+R64*$U$1</f>
         <v>559.85199999999998</v>
       </c>
@@ -12406,7 +12437,7 @@
         <f t="shared" si="5"/>
         <v>98.262678000000221</v>
       </c>
-      <c r="U65" s="5">
+      <c r="U65" s="23">
         <f t="shared" si="21"/>
         <v>157.51619800000023</v>
       </c>
@@ -12517,7 +12548,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U66" s="5">
+      <c r="U66" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -12633,7 +12664,7 @@
         <f t="shared" si="5"/>
         <v>430.0667999999996</v>
       </c>
-      <c r="U67" s="5">
+      <c r="U67" s="23">
         <f t="shared" ref="U67:U69" si="22">T67+R67*$U$1</f>
         <v>617.10371999999961</v>
       </c>
@@ -12749,7 +12780,7 @@
         <f t="shared" si="5"/>
         <v>132.64544399999988</v>
       </c>
-      <c r="U68" s="5">
+      <c r="U68" s="23">
         <f t="shared" si="22"/>
         <v>181.57771399999987</v>
       </c>
@@ -12861,7 +12892,7 @@
         <f t="shared" si="5"/>
         <v>3.8300000000000018</v>
       </c>
-      <c r="U69" s="5">
+      <c r="U69" s="23">
         <f t="shared" si="22"/>
         <v>5.9000000000000021</v>
       </c>
@@ -12970,7 +13001,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U70" s="5">
+      <c r="U70" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -13086,7 +13117,7 @@
         <f t="shared" ref="T71:T127" si="25">S71</f>
         <v>43.015999999999906</v>
       </c>
-      <c r="U71" s="5">
+      <c r="U71" s="23">
         <f t="shared" ref="U71:U72" si="26">T71+R71*$U$1</f>
         <v>69.925999999999902</v>
       </c>
@@ -13198,7 +13229,7 @@
         <f t="shared" si="25"/>
         <v>44.199999999999989</v>
       </c>
-      <c r="U72" s="5">
+      <c r="U72" s="23">
         <f t="shared" si="26"/>
         <v>51.789999999999985</v>
       </c>
@@ -13309,7 +13340,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U73" s="5">
+      <c r="U73" s="23">
         <f t="shared" ref="U73:U127" si="30">T73</f>
         <v>0</v>
       </c>
@@ -13420,7 +13451,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U74" s="5">
+      <c r="U74" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -13531,7 +13562,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U75" s="5">
+      <c r="U75" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -13643,7 +13674,7 @@
         <f t="shared" si="25"/>
         <v>389</v>
       </c>
-      <c r="U76" s="5">
+      <c r="U76" s="23">
         <f t="shared" ref="U76:U77" si="31">T76+R76*$U$1</f>
         <v>522.4</v>
       </c>
@@ -13757,7 +13788,7 @@
         <f t="shared" si="25"/>
         <v>146.39999999999998</v>
       </c>
-      <c r="U77" s="5">
+      <c r="U77" s="23">
         <f t="shared" si="31"/>
         <v>182.27999999999997</v>
       </c>
@@ -13870,7 +13901,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U78" s="5">
+      <c r="U78" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -13984,7 +14015,7 @@
         <f t="shared" si="25"/>
         <v>327.95800000000008</v>
       </c>
-      <c r="U79" s="5">
+      <c r="U79" s="23">
         <f>T79+R79*$U$1</f>
         <v>391.20800000000008</v>
       </c>
@@ -14095,7 +14126,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U80" s="5">
+      <c r="U80" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -14202,7 +14233,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U81" s="5">
+      <c r="U81" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -14300,7 +14331,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U82" s="5">
+      <c r="U82" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -14411,7 +14442,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U83" s="5">
+      <c r="U83" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -14522,7 +14553,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U84" s="5">
+      <c r="U84" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -14631,7 +14662,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U85" s="5">
+      <c r="U85" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -14745,7 +14776,7 @@
         <f t="shared" si="25"/>
         <v>109.79479999999995</v>
       </c>
-      <c r="U86" s="5">
+      <c r="U86" s="23">
         <f t="shared" ref="U86:U87" si="33">T86+R86*$U$1</f>
         <v>164.89060999999995</v>
       </c>
@@ -14859,7 +14890,7 @@
         <f t="shared" si="25"/>
         <v>376.17839999999978</v>
       </c>
-      <c r="U87" s="5">
+      <c r="U87" s="23">
         <f t="shared" si="33"/>
         <v>592.90072999999973</v>
       </c>
@@ -14970,7 +15001,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U88" s="5">
+      <c r="U88" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -15079,7 +15110,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U89" s="5">
+      <c r="U89" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -15188,7 +15219,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U90" s="5">
+      <c r="U90" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -15297,7 +15328,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U91" s="5">
+      <c r="U91" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -15402,7 +15433,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U92" s="5">
+      <c r="U92" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -15516,7 +15547,7 @@
         <f t="shared" si="25"/>
         <v>1.5298000000000016</v>
       </c>
-      <c r="U93" s="5">
+      <c r="U93" s="23">
         <f t="shared" ref="U93:U94" si="34">T93+R93*$U$1</f>
         <v>6.8455600000000008</v>
       </c>
@@ -15628,7 +15659,7 @@
         <f t="shared" si="25"/>
         <v>155</v>
       </c>
-      <c r="U94" s="5">
+      <c r="U94" s="23">
         <f t="shared" si="34"/>
         <v>201</v>
       </c>
@@ -15737,7 +15768,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U95" s="5">
+      <c r="U95" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -15846,7 +15877,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U96" s="5">
+      <c r="U96" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -15955,7 +15986,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U97" s="5">
+      <c r="U97" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -16064,7 +16095,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U98" s="5">
+      <c r="U98" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -16178,8 +16209,8 @@
         <f t="shared" si="25"/>
         <v>56.660000000000025</v>
       </c>
-      <c r="U99" s="5">
-        <f t="shared" ref="U99:U100" si="35">T99+R99*$U$1</f>
+      <c r="U99" s="23">
+        <f t="shared" ref="U99" si="35">T99+R99*$U$1</f>
         <v>78.050000000000026</v>
       </c>
       <c r="V99" s="5"/>
@@ -16292,7 +16323,7 @@
         <f t="shared" si="25"/>
         <v>108.93200000000004</v>
       </c>
-      <c r="U100" s="20">
+      <c r="U100" s="24">
         <v>0</v>
       </c>
       <c r="V100" s="5"/>
@@ -16320,7 +16351,7 @@
       <c r="AD100" s="1">
         <v>11.8</v>
       </c>
-      <c r="AE100" s="19" t="s">
+      <c r="AE100" s="18" t="s">
         <v>288</v>
       </c>
       <c r="AF100" s="1">
@@ -16402,7 +16433,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U101" s="5">
+      <c r="U101" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -16511,7 +16542,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U102" s="5">
+      <c r="U102" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -16625,7 +16656,7 @@
         <f t="shared" si="25"/>
         <v>69.799999999999955</v>
       </c>
-      <c r="U103" s="5">
+      <c r="U103" s="23">
         <f>T103+R103*$U$1</f>
         <v>108.20999999999995</v>
       </c>
@@ -16736,7 +16767,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U104" s="5">
+      <c r="U104" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -16843,7 +16874,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U105" s="5">
+      <c r="U105" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -16955,7 +16986,7 @@
         <f t="shared" si="25"/>
         <v>123.20000000000005</v>
       </c>
-      <c r="U106" s="5">
+      <c r="U106" s="23">
         <f>T106+R106*$U$1</f>
         <v>168.74000000000004</v>
       </c>
@@ -17064,7 +17095,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U107" s="5">
+      <c r="U107" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -17173,7 +17204,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U108" s="5">
+      <c r="U108" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -17284,7 +17315,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U109" s="5">
+      <c r="U109" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -17395,7 +17426,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U110" s="5">
+      <c r="U110" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -17507,7 +17538,7 @@
         <f t="shared" si="25"/>
         <v>114.31279999999992</v>
       </c>
-      <c r="U111" s="5">
+      <c r="U111" s="23">
         <f>T111+R111*$U$1</f>
         <v>237.51735999999991</v>
       </c>
@@ -17618,7 +17649,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U112" s="5">
+      <c r="U112" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -17732,7 +17763,7 @@
         <f t="shared" si="25"/>
         <v>69.400000000000091</v>
       </c>
-      <c r="U113" s="5">
+      <c r="U113" s="23">
         <f t="shared" ref="U113:U114" si="37">T113+R113*$U$1</f>
         <v>144.38000000000011</v>
       </c>
@@ -17846,7 +17877,7 @@
         <f t="shared" si="25"/>
         <v>123.40000000000009</v>
       </c>
-      <c r="U114" s="5">
+      <c r="U114" s="23">
         <f t="shared" si="37"/>
         <v>202.98000000000008</v>
       </c>
@@ -17957,7 +17988,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U115" s="5">
+      <c r="U115" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -18068,7 +18099,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U116" s="5">
+      <c r="U116" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -18177,7 +18208,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U117" s="5">
+      <c r="U117" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -18288,7 +18319,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U118" s="5">
+      <c r="U118" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -18402,7 +18433,7 @@
         <f t="shared" si="25"/>
         <v>70.251199999999983</v>
       </c>
-      <c r="U119" s="5">
+      <c r="U119" s="23">
         <f>T119+R119*$U$1</f>
         <v>105.37863999999999</v>
       </c>
@@ -18502,7 +18533,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U120" s="5">
+      <c r="U120" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -18616,7 +18647,7 @@
         <f t="shared" si="25"/>
         <v>58.400000000000091</v>
       </c>
-      <c r="U121" s="5">
+      <c r="U121" s="23">
         <f t="shared" ref="U121:U123" si="38">T121+R121*$U$1</f>
         <v>135.68000000000009</v>
       </c>
@@ -18728,7 +18759,7 @@
         <f t="shared" si="25"/>
         <v>220.79999999999995</v>
       </c>
-      <c r="U122" s="5">
+      <c r="U122" s="23">
         <f t="shared" si="38"/>
         <v>286.80999999999995</v>
       </c>
@@ -18842,7 +18873,7 @@
         <f t="shared" si="25"/>
         <v>72.949846000000008</v>
       </c>
-      <c r="U123" s="5">
+      <c r="U123" s="23">
         <f t="shared" si="38"/>
         <v>151.210106</v>
       </c>
@@ -18953,7 +18984,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U124" s="5">
+      <c r="U124" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -19062,7 +19093,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U125" s="5">
+      <c r="U125" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -19165,7 +19196,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U126" s="5">
+      <c r="U126" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -19270,7 +19301,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U127" s="5">
+      <c r="U127" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
@@ -19347,7 +19378,7 @@
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
       <c r="T128" s="1"/>
-      <c r="U128" s="1"/>
+      <c r="U128" s="20"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
       <c r="X128" s="1"/>
@@ -19402,7 +19433,7 @@
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
       <c r="T129" s="1"/>
-      <c r="U129" s="1"/>
+      <c r="U129" s="20"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
       <c r="X129" s="1"/>
@@ -19457,7 +19488,7 @@
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
       <c r="T130" s="1"/>
-      <c r="U130" s="1"/>
+      <c r="U130" s="20"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
       <c r="X130" s="1"/>
@@ -19512,7 +19543,7 @@
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
       <c r="T131" s="1"/>
-      <c r="U131" s="1"/>
+      <c r="U131" s="20"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
       <c r="X131" s="1"/>
@@ -19567,7 +19598,7 @@
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
       <c r="T132" s="1"/>
-      <c r="U132" s="1"/>
+      <c r="U132" s="20"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
       <c r="X132" s="1"/>
@@ -19622,7 +19653,7 @@
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
       <c r="T133" s="1"/>
-      <c r="U133" s="1"/>
+      <c r="U133" s="20"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
       <c r="X133" s="1"/>
@@ -19677,7 +19708,7 @@
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
       <c r="T134" s="1"/>
-      <c r="U134" s="1"/>
+      <c r="U134" s="20"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
       <c r="X134" s="1"/>
@@ -19732,7 +19763,7 @@
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
       <c r="T135" s="1"/>
-      <c r="U135" s="1"/>
+      <c r="U135" s="20"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
       <c r="X135" s="1"/>
@@ -19787,7 +19818,7 @@
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
       <c r="T136" s="1"/>
-      <c r="U136" s="1"/>
+      <c r="U136" s="20"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
       <c r="X136" s="1"/>
@@ -19842,7 +19873,7 @@
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
       <c r="T137" s="1"/>
-      <c r="U137" s="1"/>
+      <c r="U137" s="20"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
       <c r="X137" s="1"/>
@@ -19897,7 +19928,7 @@
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
       <c r="T138" s="1"/>
-      <c r="U138" s="1"/>
+      <c r="U138" s="20"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
       <c r="X138" s="1"/>
@@ -19952,7 +19983,7 @@
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
-      <c r="U139" s="1"/>
+      <c r="U139" s="20"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
       <c r="X139" s="1"/>
@@ -20007,7 +20038,7 @@
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
-      <c r="U140" s="1"/>
+      <c r="U140" s="20"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
       <c r="X140" s="1"/>
@@ -20062,7 +20093,7 @@
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
       <c r="T141" s="1"/>
-      <c r="U141" s="1"/>
+      <c r="U141" s="20"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
       <c r="X141" s="1"/>
@@ -20117,7 +20148,7 @@
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
       <c r="T142" s="1"/>
-      <c r="U142" s="1"/>
+      <c r="U142" s="20"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
       <c r="X142" s="1"/>
@@ -20172,7 +20203,7 @@
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
       <c r="T143" s="1"/>
-      <c r="U143" s="1"/>
+      <c r="U143" s="20"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
       <c r="X143" s="1"/>
@@ -20227,7 +20258,7 @@
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
       <c r="T144" s="1"/>
-      <c r="U144" s="1"/>
+      <c r="U144" s="20"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
       <c r="X144" s="1"/>
@@ -20282,7 +20313,7 @@
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
       <c r="T145" s="1"/>
-      <c r="U145" s="1"/>
+      <c r="U145" s="20"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
       <c r="X145" s="1"/>
@@ -20337,7 +20368,7 @@
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
-      <c r="U146" s="1"/>
+      <c r="U146" s="20"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
       <c r="X146" s="1"/>
@@ -20392,7 +20423,7 @@
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
-      <c r="U147" s="1"/>
+      <c r="U147" s="20"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
       <c r="X147" s="1"/>
@@ -20447,7 +20478,7 @@
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
       <c r="T148" s="1"/>
-      <c r="U148" s="1"/>
+      <c r="U148" s="20"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
       <c r="X148" s="1"/>
@@ -20502,7 +20533,7 @@
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
-      <c r="U149" s="1"/>
+      <c r="U149" s="20"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
       <c r="X149" s="1"/>
@@ -20557,7 +20588,7 @@
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
       <c r="T150" s="1"/>
-      <c r="U150" s="1"/>
+      <c r="U150" s="20"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
       <c r="X150" s="1"/>
@@ -20612,7 +20643,7 @@
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
       <c r="T151" s="1"/>
-      <c r="U151" s="1"/>
+      <c r="U151" s="20"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
       <c r="X151" s="1"/>
@@ -20667,7 +20698,7 @@
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
       <c r="T152" s="1"/>
-      <c r="U152" s="1"/>
+      <c r="U152" s="20"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
       <c r="X152" s="1"/>
@@ -20722,7 +20753,7 @@
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
       <c r="T153" s="1"/>
-      <c r="U153" s="1"/>
+      <c r="U153" s="20"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
       <c r="X153" s="1"/>
@@ -20777,7 +20808,7 @@
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
       <c r="T154" s="1"/>
-      <c r="U154" s="1"/>
+      <c r="U154" s="20"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
       <c r="X154" s="1"/>
@@ -20832,7 +20863,7 @@
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
       <c r="T155" s="1"/>
-      <c r="U155" s="1"/>
+      <c r="U155" s="20"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
       <c r="X155" s="1"/>
@@ -20887,7 +20918,7 @@
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
       <c r="T156" s="1"/>
-      <c r="U156" s="1"/>
+      <c r="U156" s="20"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
       <c r="X156" s="1"/>
@@ -20942,7 +20973,7 @@
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
       <c r="T157" s="1"/>
-      <c r="U157" s="1"/>
+      <c r="U157" s="20"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
       <c r="X157" s="1"/>
@@ -20997,7 +21028,7 @@
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
       <c r="T158" s="1"/>
-      <c r="U158" s="1"/>
+      <c r="U158" s="20"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
       <c r="X158" s="1"/>
@@ -21052,7 +21083,7 @@
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
       <c r="T159" s="1"/>
-      <c r="U159" s="1"/>
+      <c r="U159" s="20"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
       <c r="X159" s="1"/>
@@ -21107,7 +21138,7 @@
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
       <c r="T160" s="1"/>
-      <c r="U160" s="1"/>
+      <c r="U160" s="20"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
       <c r="X160" s="1"/>
@@ -21162,7 +21193,7 @@
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
       <c r="T161" s="1"/>
-      <c r="U161" s="1"/>
+      <c r="U161" s="20"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
       <c r="X161" s="1"/>
@@ -21217,7 +21248,7 @@
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
       <c r="T162" s="1"/>
-      <c r="U162" s="1"/>
+      <c r="U162" s="20"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
       <c r="X162" s="1"/>
@@ -21272,7 +21303,7 @@
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
       <c r="T163" s="1"/>
-      <c r="U163" s="1"/>
+      <c r="U163" s="20"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
       <c r="X163" s="1"/>
@@ -21327,7 +21358,7 @@
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
       <c r="T164" s="1"/>
-      <c r="U164" s="1"/>
+      <c r="U164" s="20"/>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
       <c r="X164" s="1"/>
@@ -21382,7 +21413,7 @@
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
       <c r="T165" s="1"/>
-      <c r="U165" s="1"/>
+      <c r="U165" s="20"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
       <c r="X165" s="1"/>
@@ -21437,7 +21468,7 @@
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
       <c r="T166" s="1"/>
-      <c r="U166" s="1"/>
+      <c r="U166" s="20"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
       <c r="X166" s="1"/>
@@ -21492,7 +21523,7 @@
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
       <c r="T167" s="1"/>
-      <c r="U167" s="1"/>
+      <c r="U167" s="20"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
       <c r="X167" s="1"/>
@@ -21547,7 +21578,7 @@
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
       <c r="T168" s="1"/>
-      <c r="U168" s="1"/>
+      <c r="U168" s="20"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
       <c r="X168" s="1"/>
@@ -21602,7 +21633,7 @@
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
-      <c r="U169" s="1"/>
+      <c r="U169" s="20"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
       <c r="X169" s="1"/>
@@ -21657,7 +21688,7 @@
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
       <c r="T170" s="1"/>
-      <c r="U170" s="1"/>
+      <c r="U170" s="20"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
       <c r="X170" s="1"/>
@@ -21712,7 +21743,7 @@
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
       <c r="T171" s="1"/>
-      <c r="U171" s="1"/>
+      <c r="U171" s="20"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
       <c r="X171" s="1"/>
@@ -21767,7 +21798,7 @@
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
       <c r="T172" s="1"/>
-      <c r="U172" s="1"/>
+      <c r="U172" s="20"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
       <c r="X172" s="1"/>
@@ -21822,7 +21853,7 @@
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
       <c r="T173" s="1"/>
-      <c r="U173" s="1"/>
+      <c r="U173" s="20"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
       <c r="X173" s="1"/>
@@ -21877,7 +21908,7 @@
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
       <c r="T174" s="1"/>
-      <c r="U174" s="1"/>
+      <c r="U174" s="20"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
       <c r="X174" s="1"/>
@@ -21932,7 +21963,7 @@
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
       <c r="T175" s="1"/>
-      <c r="U175" s="1"/>
+      <c r="U175" s="20"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
       <c r="X175" s="1"/>
@@ -21987,7 +22018,7 @@
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
       <c r="T176" s="1"/>
-      <c r="U176" s="1"/>
+      <c r="U176" s="20"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
       <c r="X176" s="1"/>
@@ -22042,7 +22073,7 @@
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
       <c r="T177" s="1"/>
-      <c r="U177" s="1"/>
+      <c r="U177" s="20"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
       <c r="X177" s="1"/>
@@ -22097,7 +22128,7 @@
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
       <c r="T178" s="1"/>
-      <c r="U178" s="1"/>
+      <c r="U178" s="20"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
       <c r="X178" s="1"/>
@@ -22152,7 +22183,7 @@
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
       <c r="T179" s="1"/>
-      <c r="U179" s="1"/>
+      <c r="U179" s="20"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
       <c r="X179" s="1"/>
@@ -22207,7 +22238,7 @@
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
       <c r="T180" s="1"/>
-      <c r="U180" s="1"/>
+      <c r="U180" s="20"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
       <c r="X180" s="1"/>
@@ -22262,7 +22293,7 @@
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
-      <c r="U181" s="1"/>
+      <c r="U181" s="20"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
       <c r="X181" s="1"/>
@@ -22317,7 +22348,7 @@
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
       <c r="T182" s="1"/>
-      <c r="U182" s="1"/>
+      <c r="U182" s="20"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
       <c r="X182" s="1"/>
@@ -22372,7 +22403,7 @@
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
       <c r="T183" s="1"/>
-      <c r="U183" s="1"/>
+      <c r="U183" s="20"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
       <c r="X183" s="1"/>
@@ -22427,7 +22458,7 @@
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
       <c r="T184" s="1"/>
-      <c r="U184" s="1"/>
+      <c r="U184" s="20"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
       <c r="X184" s="1"/>
@@ -22482,7 +22513,7 @@
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
       <c r="T185" s="1"/>
-      <c r="U185" s="1"/>
+      <c r="U185" s="20"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
       <c r="X185" s="1"/>
@@ -22537,7 +22568,7 @@
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
       <c r="T186" s="1"/>
-      <c r="U186" s="1"/>
+      <c r="U186" s="20"/>
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
       <c r="X186" s="1"/>
@@ -22592,7 +22623,7 @@
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
       <c r="T187" s="1"/>
-      <c r="U187" s="1"/>
+      <c r="U187" s="20"/>
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
       <c r="X187" s="1"/>
@@ -22647,7 +22678,7 @@
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
       <c r="T188" s="1"/>
-      <c r="U188" s="1"/>
+      <c r="U188" s="20"/>
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
       <c r="X188" s="1"/>
@@ -22702,7 +22733,7 @@
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
       <c r="T189" s="1"/>
-      <c r="U189" s="1"/>
+      <c r="U189" s="20"/>
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
       <c r="X189" s="1"/>
@@ -22757,7 +22788,7 @@
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
       <c r="T190" s="1"/>
-      <c r="U190" s="1"/>
+      <c r="U190" s="20"/>
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
       <c r="X190" s="1"/>
@@ -22812,7 +22843,7 @@
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
       <c r="T191" s="1"/>
-      <c r="U191" s="1"/>
+      <c r="U191" s="20"/>
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
       <c r="X191" s="1"/>
@@ -22867,7 +22898,7 @@
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
       <c r="T192" s="1"/>
-      <c r="U192" s="1"/>
+      <c r="U192" s="20"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
       <c r="X192" s="1"/>
@@ -22922,7 +22953,7 @@
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
       <c r="T193" s="1"/>
-      <c r="U193" s="1"/>
+      <c r="U193" s="20"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
       <c r="X193" s="1"/>
@@ -22977,7 +23008,7 @@
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
       <c r="T194" s="1"/>
-      <c r="U194" s="1"/>
+      <c r="U194" s="20"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
       <c r="X194" s="1"/>
@@ -23032,7 +23063,7 @@
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
       <c r="T195" s="1"/>
-      <c r="U195" s="1"/>
+      <c r="U195" s="20"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
       <c r="X195" s="1"/>
@@ -23087,7 +23118,7 @@
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
       <c r="T196" s="1"/>
-      <c r="U196" s="1"/>
+      <c r="U196" s="20"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
       <c r="X196" s="1"/>
@@ -23142,7 +23173,7 @@
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
       <c r="T197" s="1"/>
-      <c r="U197" s="1"/>
+      <c r="U197" s="20"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
       <c r="X197" s="1"/>
@@ -23197,7 +23228,7 @@
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
       <c r="T198" s="1"/>
-      <c r="U198" s="1"/>
+      <c r="U198" s="20"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
       <c r="X198" s="1"/>
@@ -23252,7 +23283,7 @@
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
       <c r="T199" s="1"/>
-      <c r="U199" s="1"/>
+      <c r="U199" s="20"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
       <c r="X199" s="1"/>
@@ -23307,7 +23338,7 @@
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
       <c r="T200" s="1"/>
-      <c r="U200" s="1"/>
+      <c r="U200" s="20"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
       <c r="X200" s="1"/>
@@ -23362,7 +23393,7 @@
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
       <c r="T201" s="1"/>
-      <c r="U201" s="1"/>
+      <c r="U201" s="20"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
       <c r="X201" s="1"/>
@@ -23417,7 +23448,7 @@
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
       <c r="T202" s="1"/>
-      <c r="U202" s="1"/>
+      <c r="U202" s="20"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
       <c r="X202" s="1"/>
@@ -23472,7 +23503,7 @@
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
       <c r="T203" s="1"/>
-      <c r="U203" s="1"/>
+      <c r="U203" s="20"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
       <c r="X203" s="1"/>
@@ -23527,7 +23558,7 @@
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
       <c r="T204" s="1"/>
-      <c r="U204" s="1"/>
+      <c r="U204" s="20"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
       <c r="X204" s="1"/>
@@ -23582,7 +23613,7 @@
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
       <c r="T205" s="1"/>
-      <c r="U205" s="1"/>
+      <c r="U205" s="20"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
       <c r="X205" s="1"/>
@@ -23637,7 +23668,7 @@
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
       <c r="T206" s="1"/>
-      <c r="U206" s="1"/>
+      <c r="U206" s="20"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
       <c r="X206" s="1"/>
@@ -23692,7 +23723,7 @@
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
       <c r="T207" s="1"/>
-      <c r="U207" s="1"/>
+      <c r="U207" s="20"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
       <c r="X207" s="1"/>
@@ -23747,7 +23778,7 @@
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
       <c r="T208" s="1"/>
-      <c r="U208" s="1"/>
+      <c r="U208" s="20"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
       <c r="X208" s="1"/>
@@ -23802,7 +23833,7 @@
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
       <c r="T209" s="1"/>
-      <c r="U209" s="1"/>
+      <c r="U209" s="20"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
       <c r="X209" s="1"/>
@@ -23857,7 +23888,7 @@
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
       <c r="T210" s="1"/>
-      <c r="U210" s="1"/>
+      <c r="U210" s="20"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
       <c r="X210" s="1"/>
@@ -23912,7 +23943,7 @@
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
       <c r="T211" s="1"/>
-      <c r="U211" s="1"/>
+      <c r="U211" s="20"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
       <c r="X211" s="1"/>
@@ -23967,7 +23998,7 @@
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
       <c r="T212" s="1"/>
-      <c r="U212" s="1"/>
+      <c r="U212" s="20"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
       <c r="X212" s="1"/>
@@ -24022,7 +24053,7 @@
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
       <c r="T213" s="1"/>
-      <c r="U213" s="1"/>
+      <c r="U213" s="20"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
       <c r="X213" s="1"/>
@@ -24077,7 +24108,7 @@
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
       <c r="T214" s="1"/>
-      <c r="U214" s="1"/>
+      <c r="U214" s="20"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
       <c r="X214" s="1"/>
@@ -24132,7 +24163,7 @@
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
       <c r="T215" s="1"/>
-      <c r="U215" s="1"/>
+      <c r="U215" s="20"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
       <c r="X215" s="1"/>
@@ -24187,7 +24218,7 @@
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
       <c r="T216" s="1"/>
-      <c r="U216" s="1"/>
+      <c r="U216" s="20"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
       <c r="X216" s="1"/>
@@ -24242,7 +24273,7 @@
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
       <c r="T217" s="1"/>
-      <c r="U217" s="1"/>
+      <c r="U217" s="20"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
       <c r="X217" s="1"/>
@@ -24297,7 +24328,7 @@
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
       <c r="T218" s="1"/>
-      <c r="U218" s="1"/>
+      <c r="U218" s="20"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
       <c r="X218" s="1"/>
@@ -24352,7 +24383,7 @@
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
       <c r="T219" s="1"/>
-      <c r="U219" s="1"/>
+      <c r="U219" s="20"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
       <c r="X219" s="1"/>
@@ -24407,7 +24438,7 @@
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
       <c r="T220" s="1"/>
-      <c r="U220" s="1"/>
+      <c r="U220" s="20"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
       <c r="X220" s="1"/>
@@ -24462,7 +24493,7 @@
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
       <c r="T221" s="1"/>
-      <c r="U221" s="1"/>
+      <c r="U221" s="20"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
       <c r="X221" s="1"/>
@@ -24517,7 +24548,7 @@
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
       <c r="T222" s="1"/>
-      <c r="U222" s="1"/>
+      <c r="U222" s="20"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
       <c r="X222" s="1"/>
@@ -24572,7 +24603,7 @@
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
       <c r="T223" s="1"/>
-      <c r="U223" s="1"/>
+      <c r="U223" s="20"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
       <c r="X223" s="1"/>
@@ -24627,7 +24658,7 @@
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
       <c r="T224" s="1"/>
-      <c r="U224" s="1"/>
+      <c r="U224" s="20"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
       <c r="X224" s="1"/>
@@ -24682,7 +24713,7 @@
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
       <c r="T225" s="1"/>
-      <c r="U225" s="1"/>
+      <c r="U225" s="20"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
       <c r="X225" s="1"/>
@@ -24737,7 +24768,7 @@
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
       <c r="T226" s="1"/>
-      <c r="U226" s="1"/>
+      <c r="U226" s="20"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
       <c r="X226" s="1"/>
@@ -24792,7 +24823,7 @@
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
       <c r="T227" s="1"/>
-      <c r="U227" s="1"/>
+      <c r="U227" s="20"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
       <c r="X227" s="1"/>
@@ -24847,7 +24878,7 @@
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
       <c r="T228" s="1"/>
-      <c r="U228" s="1"/>
+      <c r="U228" s="20"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
       <c r="X228" s="1"/>
@@ -24902,7 +24933,7 @@
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
       <c r="T229" s="1"/>
-      <c r="U229" s="1"/>
+      <c r="U229" s="20"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
       <c r="X229" s="1"/>
@@ -24957,7 +24988,7 @@
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
       <c r="T230" s="1"/>
-      <c r="U230" s="1"/>
+      <c r="U230" s="20"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
       <c r="X230" s="1"/>
@@ -25012,7 +25043,7 @@
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
       <c r="T231" s="1"/>
-      <c r="U231" s="1"/>
+      <c r="U231" s="20"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
       <c r="X231" s="1"/>
@@ -25067,7 +25098,7 @@
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
       <c r="T232" s="1"/>
-      <c r="U232" s="1"/>
+      <c r="U232" s="20"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
       <c r="X232" s="1"/>
@@ -25122,7 +25153,7 @@
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
       <c r="T233" s="1"/>
-      <c r="U233" s="1"/>
+      <c r="U233" s="20"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
       <c r="X233" s="1"/>
@@ -25177,7 +25208,7 @@
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
       <c r="T234" s="1"/>
-      <c r="U234" s="1"/>
+      <c r="U234" s="20"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
       <c r="X234" s="1"/>
@@ -25232,7 +25263,7 @@
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
       <c r="T235" s="1"/>
-      <c r="U235" s="1"/>
+      <c r="U235" s="20"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
       <c r="X235" s="1"/>
@@ -25287,7 +25318,7 @@
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
       <c r="T236" s="1"/>
-      <c r="U236" s="1"/>
+      <c r="U236" s="20"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
       <c r="X236" s="1"/>
@@ -25342,7 +25373,7 @@
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
       <c r="T237" s="1"/>
-      <c r="U237" s="1"/>
+      <c r="U237" s="20"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
       <c r="X237" s="1"/>
@@ -25397,7 +25428,7 @@
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
       <c r="T238" s="1"/>
-      <c r="U238" s="1"/>
+      <c r="U238" s="20"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
       <c r="X238" s="1"/>
@@ -25452,7 +25483,7 @@
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
       <c r="T239" s="1"/>
-      <c r="U239" s="1"/>
+      <c r="U239" s="20"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
       <c r="X239" s="1"/>
@@ -25507,7 +25538,7 @@
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
       <c r="T240" s="1"/>
-      <c r="U240" s="1"/>
+      <c r="U240" s="20"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
       <c r="X240" s="1"/>
@@ -25562,7 +25593,7 @@
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
       <c r="T241" s="1"/>
-      <c r="U241" s="1"/>
+      <c r="U241" s="20"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
       <c r="X241" s="1"/>
@@ -25617,7 +25648,7 @@
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
       <c r="T242" s="1"/>
-      <c r="U242" s="1"/>
+      <c r="U242" s="20"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
       <c r="X242" s="1"/>
@@ -25672,7 +25703,7 @@
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
       <c r="T243" s="1"/>
-      <c r="U243" s="1"/>
+      <c r="U243" s="20"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
       <c r="X243" s="1"/>
@@ -25727,7 +25758,7 @@
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
       <c r="T244" s="1"/>
-      <c r="U244" s="1"/>
+      <c r="U244" s="20"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
       <c r="X244" s="1"/>
@@ -25782,7 +25813,7 @@
       <c r="R245" s="1"/>
       <c r="S245" s="1"/>
       <c r="T245" s="1"/>
-      <c r="U245" s="1"/>
+      <c r="U245" s="20"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
       <c r="X245" s="1"/>
@@ -25837,7 +25868,7 @@
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
       <c r="T246" s="1"/>
-      <c r="U246" s="1"/>
+      <c r="U246" s="20"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
       <c r="X246" s="1"/>
@@ -25892,7 +25923,7 @@
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
       <c r="T247" s="1"/>
-      <c r="U247" s="1"/>
+      <c r="U247" s="20"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
       <c r="X247" s="1"/>
@@ -25947,7 +25978,7 @@
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
       <c r="T248" s="1"/>
-      <c r="U248" s="1"/>
+      <c r="U248" s="20"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
       <c r="X248" s="1"/>
@@ -26002,7 +26033,7 @@
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
       <c r="T249" s="1"/>
-      <c r="U249" s="1"/>
+      <c r="U249" s="20"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
       <c r="X249" s="1"/>
@@ -26057,7 +26088,7 @@
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
       <c r="T250" s="1"/>
-      <c r="U250" s="1"/>
+      <c r="U250" s="20"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
       <c r="X250" s="1"/>
@@ -26112,7 +26143,7 @@
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
       <c r="T251" s="1"/>
-      <c r="U251" s="1"/>
+      <c r="U251" s="20"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
       <c r="X251" s="1"/>
@@ -26167,7 +26198,7 @@
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
       <c r="T252" s="1"/>
-      <c r="U252" s="1"/>
+      <c r="U252" s="20"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
       <c r="X252" s="1"/>
@@ -26222,7 +26253,7 @@
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
       <c r="T253" s="1"/>
-      <c r="U253" s="1"/>
+      <c r="U253" s="20"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
       <c r="X253" s="1"/>
@@ -26277,7 +26308,7 @@
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
       <c r="T254" s="1"/>
-      <c r="U254" s="1"/>
+      <c r="U254" s="20"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
       <c r="X254" s="1"/>
@@ -26332,7 +26363,7 @@
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
       <c r="T255" s="1"/>
-      <c r="U255" s="1"/>
+      <c r="U255" s="20"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
       <c r="X255" s="1"/>
@@ -26387,7 +26418,7 @@
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
       <c r="T256" s="1"/>
-      <c r="U256" s="1"/>
+      <c r="U256" s="20"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
       <c r="X256" s="1"/>
@@ -26442,7 +26473,7 @@
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
       <c r="T257" s="1"/>
-      <c r="U257" s="1"/>
+      <c r="U257" s="20"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
       <c r="X257" s="1"/>
@@ -26497,7 +26528,7 @@
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
       <c r="T258" s="1"/>
-      <c r="U258" s="1"/>
+      <c r="U258" s="20"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
       <c r="X258" s="1"/>
@@ -26552,7 +26583,7 @@
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
       <c r="T259" s="1"/>
-      <c r="U259" s="1"/>
+      <c r="U259" s="20"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
       <c r="X259" s="1"/>
@@ -26607,7 +26638,7 @@
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
       <c r="T260" s="1"/>
-      <c r="U260" s="1"/>
+      <c r="U260" s="20"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
       <c r="X260" s="1"/>
@@ -26662,7 +26693,7 @@
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
       <c r="T261" s="1"/>
-      <c r="U261" s="1"/>
+      <c r="U261" s="20"/>
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
       <c r="X261" s="1"/>
@@ -26717,7 +26748,7 @@
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
       <c r="T262" s="1"/>
-      <c r="U262" s="1"/>
+      <c r="U262" s="20"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
       <c r="X262" s="1"/>
@@ -26772,7 +26803,7 @@
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
       <c r="T263" s="1"/>
-      <c r="U263" s="1"/>
+      <c r="U263" s="20"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
       <c r="X263" s="1"/>
@@ -26827,7 +26858,7 @@
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
       <c r="T264" s="1"/>
-      <c r="U264" s="1"/>
+      <c r="U264" s="20"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
       <c r="X264" s="1"/>
@@ -26882,7 +26913,7 @@
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
       <c r="T265" s="1"/>
-      <c r="U265" s="1"/>
+      <c r="U265" s="20"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
       <c r="X265" s="1"/>
@@ -26937,7 +26968,7 @@
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
       <c r="T266" s="1"/>
-      <c r="U266" s="1"/>
+      <c r="U266" s="20"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
       <c r="X266" s="1"/>
@@ -26992,7 +27023,7 @@
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
       <c r="T267" s="1"/>
-      <c r="U267" s="1"/>
+      <c r="U267" s="20"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
       <c r="X267" s="1"/>
@@ -27047,7 +27078,7 @@
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
       <c r="T268" s="1"/>
-      <c r="U268" s="1"/>
+      <c r="U268" s="20"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
       <c r="X268" s="1"/>
@@ -27102,7 +27133,7 @@
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
       <c r="T269" s="1"/>
-      <c r="U269" s="1"/>
+      <c r="U269" s="20"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
       <c r="X269" s="1"/>
@@ -27157,7 +27188,7 @@
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
       <c r="T270" s="1"/>
-      <c r="U270" s="1"/>
+      <c r="U270" s="20"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
       <c r="X270" s="1"/>
@@ -27212,7 +27243,7 @@
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
       <c r="T271" s="1"/>
-      <c r="U271" s="1"/>
+      <c r="U271" s="20"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
       <c r="X271" s="1"/>
@@ -27267,7 +27298,7 @@
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
       <c r="T272" s="1"/>
-      <c r="U272" s="1"/>
+      <c r="U272" s="20"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
       <c r="X272" s="1"/>
@@ -27322,7 +27353,7 @@
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
       <c r="T273" s="1"/>
-      <c r="U273" s="1"/>
+      <c r="U273" s="20"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
       <c r="X273" s="1"/>
@@ -27377,7 +27408,7 @@
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
       <c r="T274" s="1"/>
-      <c r="U274" s="1"/>
+      <c r="U274" s="20"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
       <c r="X274" s="1"/>
@@ -27432,7 +27463,7 @@
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
       <c r="T275" s="1"/>
-      <c r="U275" s="1"/>
+      <c r="U275" s="20"/>
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
       <c r="X275" s="1"/>
@@ -27487,7 +27518,7 @@
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
       <c r="T276" s="1"/>
-      <c r="U276" s="1"/>
+      <c r="U276" s="20"/>
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
       <c r="X276" s="1"/>
@@ -27542,7 +27573,7 @@
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
       <c r="T277" s="1"/>
-      <c r="U277" s="1"/>
+      <c r="U277" s="20"/>
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
       <c r="X277" s="1"/>
@@ -27597,7 +27628,7 @@
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
       <c r="T278" s="1"/>
-      <c r="U278" s="1"/>
+      <c r="U278" s="20"/>
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
       <c r="X278" s="1"/>
@@ -27652,7 +27683,7 @@
       <c r="R279" s="1"/>
       <c r="S279" s="1"/>
       <c r="T279" s="1"/>
-      <c r="U279" s="1"/>
+      <c r="U279" s="20"/>
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
       <c r="X279" s="1"/>
@@ -27707,7 +27738,7 @@
       <c r="R280" s="1"/>
       <c r="S280" s="1"/>
       <c r="T280" s="1"/>
-      <c r="U280" s="1"/>
+      <c r="U280" s="20"/>
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
       <c r="X280" s="1"/>
@@ -27762,7 +27793,7 @@
       <c r="R281" s="1"/>
       <c r="S281" s="1"/>
       <c r="T281" s="1"/>
-      <c r="U281" s="1"/>
+      <c r="U281" s="20"/>
       <c r="V281" s="1"/>
       <c r="W281" s="1"/>
       <c r="X281" s="1"/>
@@ -27817,7 +27848,7 @@
       <c r="R282" s="1"/>
       <c r="S282" s="1"/>
       <c r="T282" s="1"/>
-      <c r="U282" s="1"/>
+      <c r="U282" s="20"/>
       <c r="V282" s="1"/>
       <c r="W282" s="1"/>
       <c r="X282" s="1"/>
@@ -27872,7 +27903,7 @@
       <c r="R283" s="1"/>
       <c r="S283" s="1"/>
       <c r="T283" s="1"/>
-      <c r="U283" s="1"/>
+      <c r="U283" s="20"/>
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
       <c r="X283" s="1"/>
@@ -27927,7 +27958,7 @@
       <c r="R284" s="1"/>
       <c r="S284" s="1"/>
       <c r="T284" s="1"/>
-      <c r="U284" s="1"/>
+      <c r="U284" s="20"/>
       <c r="V284" s="1"/>
       <c r="W284" s="1"/>
       <c r="X284" s="1"/>
@@ -27982,7 +28013,7 @@
       <c r="R285" s="1"/>
       <c r="S285" s="1"/>
       <c r="T285" s="1"/>
-      <c r="U285" s="1"/>
+      <c r="U285" s="20"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
       <c r="X285" s="1"/>
@@ -28037,7 +28068,7 @@
       <c r="R286" s="1"/>
       <c r="S286" s="1"/>
       <c r="T286" s="1"/>
-      <c r="U286" s="1"/>
+      <c r="U286" s="20"/>
       <c r="V286" s="1"/>
       <c r="W286" s="1"/>
       <c r="X286" s="1"/>
@@ -28092,7 +28123,7 @@
       <c r="R287" s="1"/>
       <c r="S287" s="1"/>
       <c r="T287" s="1"/>
-      <c r="U287" s="1"/>
+      <c r="U287" s="20"/>
       <c r="V287" s="1"/>
       <c r="W287" s="1"/>
       <c r="X287" s="1"/>
@@ -28147,7 +28178,7 @@
       <c r="R288" s="1"/>
       <c r="S288" s="1"/>
       <c r="T288" s="1"/>
-      <c r="U288" s="1"/>
+      <c r="U288" s="20"/>
       <c r="V288" s="1"/>
       <c r="W288" s="1"/>
       <c r="X288" s="1"/>
@@ -28202,7 +28233,7 @@
       <c r="R289" s="1"/>
       <c r="S289" s="1"/>
       <c r="T289" s="1"/>
-      <c r="U289" s="1"/>
+      <c r="U289" s="20"/>
       <c r="V289" s="1"/>
       <c r="W289" s="1"/>
       <c r="X289" s="1"/>
@@ -28257,7 +28288,7 @@
       <c r="R290" s="1"/>
       <c r="S290" s="1"/>
       <c r="T290" s="1"/>
-      <c r="U290" s="1"/>
+      <c r="U290" s="20"/>
       <c r="V290" s="1"/>
       <c r="W290" s="1"/>
       <c r="X290" s="1"/>
@@ -28312,7 +28343,7 @@
       <c r="R291" s="1"/>
       <c r="S291" s="1"/>
       <c r="T291" s="1"/>
-      <c r="U291" s="1"/>
+      <c r="U291" s="20"/>
       <c r="V291" s="1"/>
       <c r="W291" s="1"/>
       <c r="X291" s="1"/>
@@ -28367,7 +28398,7 @@
       <c r="R292" s="1"/>
       <c r="S292" s="1"/>
       <c r="T292" s="1"/>
-      <c r="U292" s="1"/>
+      <c r="U292" s="20"/>
       <c r="V292" s="1"/>
       <c r="W292" s="1"/>
       <c r="X292" s="1"/>
@@ -28422,7 +28453,7 @@
       <c r="R293" s="1"/>
       <c r="S293" s="1"/>
       <c r="T293" s="1"/>
-      <c r="U293" s="1"/>
+      <c r="U293" s="20"/>
       <c r="V293" s="1"/>
       <c r="W293" s="1"/>
       <c r="X293" s="1"/>
@@ -28477,7 +28508,7 @@
       <c r="R294" s="1"/>
       <c r="S294" s="1"/>
       <c r="T294" s="1"/>
-      <c r="U294" s="1"/>
+      <c r="U294" s="20"/>
       <c r="V294" s="1"/>
       <c r="W294" s="1"/>
       <c r="X294" s="1"/>
@@ -28532,7 +28563,7 @@
       <c r="R295" s="1"/>
       <c r="S295" s="1"/>
       <c r="T295" s="1"/>
-      <c r="U295" s="1"/>
+      <c r="U295" s="20"/>
       <c r="V295" s="1"/>
       <c r="W295" s="1"/>
       <c r="X295" s="1"/>
@@ -28587,7 +28618,7 @@
       <c r="R296" s="1"/>
       <c r="S296" s="1"/>
       <c r="T296" s="1"/>
-      <c r="U296" s="1"/>
+      <c r="U296" s="20"/>
       <c r="V296" s="1"/>
       <c r="W296" s="1"/>
       <c r="X296" s="1"/>
@@ -28642,7 +28673,7 @@
       <c r="R297" s="1"/>
       <c r="S297" s="1"/>
       <c r="T297" s="1"/>
-      <c r="U297" s="1"/>
+      <c r="U297" s="20"/>
       <c r="V297" s="1"/>
       <c r="W297" s="1"/>
       <c r="X297" s="1"/>
@@ -28697,7 +28728,7 @@
       <c r="R298" s="1"/>
       <c r="S298" s="1"/>
       <c r="T298" s="1"/>
-      <c r="U298" s="1"/>
+      <c r="U298" s="20"/>
       <c r="V298" s="1"/>
       <c r="W298" s="1"/>
       <c r="X298" s="1"/>
@@ -28752,7 +28783,7 @@
       <c r="R299" s="1"/>
       <c r="S299" s="1"/>
       <c r="T299" s="1"/>
-      <c r="U299" s="1"/>
+      <c r="U299" s="20"/>
       <c r="V299" s="1"/>
       <c r="W299" s="1"/>
       <c r="X299" s="1"/>
@@ -28807,7 +28838,7 @@
       <c r="R300" s="1"/>
       <c r="S300" s="1"/>
       <c r="T300" s="1"/>
-      <c r="U300" s="1"/>
+      <c r="U300" s="20"/>
       <c r="V300" s="1"/>
       <c r="W300" s="1"/>
       <c r="X300" s="1"/>
@@ -28862,7 +28893,7 @@
       <c r="R301" s="1"/>
       <c r="S301" s="1"/>
       <c r="T301" s="1"/>
-      <c r="U301" s="1"/>
+      <c r="U301" s="20"/>
       <c r="V301" s="1"/>
       <c r="W301" s="1"/>
       <c r="X301" s="1"/>
@@ -28917,7 +28948,7 @@
       <c r="R302" s="1"/>
       <c r="S302" s="1"/>
       <c r="T302" s="1"/>
-      <c r="U302" s="1"/>
+      <c r="U302" s="20"/>
       <c r="V302" s="1"/>
       <c r="W302" s="1"/>
       <c r="X302" s="1"/>
@@ -28972,7 +29003,7 @@
       <c r="R303" s="1"/>
       <c r="S303" s="1"/>
       <c r="T303" s="1"/>
-      <c r="U303" s="1"/>
+      <c r="U303" s="20"/>
       <c r="V303" s="1"/>
       <c r="W303" s="1"/>
       <c r="X303" s="1"/>
@@ -29027,7 +29058,7 @@
       <c r="R304" s="1"/>
       <c r="S304" s="1"/>
       <c r="T304" s="1"/>
-      <c r="U304" s="1"/>
+      <c r="U304" s="20"/>
       <c r="V304" s="1"/>
       <c r="W304" s="1"/>
       <c r="X304" s="1"/>
@@ -29082,7 +29113,7 @@
       <c r="R305" s="1"/>
       <c r="S305" s="1"/>
       <c r="T305" s="1"/>
-      <c r="U305" s="1"/>
+      <c r="U305" s="20"/>
       <c r="V305" s="1"/>
       <c r="W305" s="1"/>
       <c r="X305" s="1"/>
@@ -29137,7 +29168,7 @@
       <c r="R306" s="1"/>
       <c r="S306" s="1"/>
       <c r="T306" s="1"/>
-      <c r="U306" s="1"/>
+      <c r="U306" s="20"/>
       <c r="V306" s="1"/>
       <c r="W306" s="1"/>
       <c r="X306" s="1"/>
@@ -29192,7 +29223,7 @@
       <c r="R307" s="1"/>
       <c r="S307" s="1"/>
       <c r="T307" s="1"/>
-      <c r="U307" s="1"/>
+      <c r="U307" s="20"/>
       <c r="V307" s="1"/>
       <c r="W307" s="1"/>
       <c r="X307" s="1"/>
@@ -29247,7 +29278,7 @@
       <c r="R308" s="1"/>
       <c r="S308" s="1"/>
       <c r="T308" s="1"/>
-      <c r="U308" s="1"/>
+      <c r="U308" s="20"/>
       <c r="V308" s="1"/>
       <c r="W308" s="1"/>
       <c r="X308" s="1"/>
@@ -29302,7 +29333,7 @@
       <c r="R309" s="1"/>
       <c r="S309" s="1"/>
       <c r="T309" s="1"/>
-      <c r="U309" s="1"/>
+      <c r="U309" s="20"/>
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
       <c r="X309" s="1"/>
@@ -29357,7 +29388,7 @@
       <c r="R310" s="1"/>
       <c r="S310" s="1"/>
       <c r="T310" s="1"/>
-      <c r="U310" s="1"/>
+      <c r="U310" s="20"/>
       <c r="V310" s="1"/>
       <c r="W310" s="1"/>
       <c r="X310" s="1"/>
@@ -29412,7 +29443,7 @@
       <c r="R311" s="1"/>
       <c r="S311" s="1"/>
       <c r="T311" s="1"/>
-      <c r="U311" s="1"/>
+      <c r="U311" s="20"/>
       <c r="V311" s="1"/>
       <c r="W311" s="1"/>
       <c r="X311" s="1"/>
@@ -29467,7 +29498,7 @@
       <c r="R312" s="1"/>
       <c r="S312" s="1"/>
       <c r="T312" s="1"/>
-      <c r="U312" s="1"/>
+      <c r="U312" s="20"/>
       <c r="V312" s="1"/>
       <c r="W312" s="1"/>
       <c r="X312" s="1"/>
@@ -29522,7 +29553,7 @@
       <c r="R313" s="1"/>
       <c r="S313" s="1"/>
       <c r="T313" s="1"/>
-      <c r="U313" s="1"/>
+      <c r="U313" s="20"/>
       <c r="V313" s="1"/>
       <c r="W313" s="1"/>
       <c r="X313" s="1"/>
@@ -29577,7 +29608,7 @@
       <c r="R314" s="1"/>
       <c r="S314" s="1"/>
       <c r="T314" s="1"/>
-      <c r="U314" s="1"/>
+      <c r="U314" s="20"/>
       <c r="V314" s="1"/>
       <c r="W314" s="1"/>
       <c r="X314" s="1"/>
@@ -29632,7 +29663,7 @@
       <c r="R315" s="1"/>
       <c r="S315" s="1"/>
       <c r="T315" s="1"/>
-      <c r="U315" s="1"/>
+      <c r="U315" s="20"/>
       <c r="V315" s="1"/>
       <c r="W315" s="1"/>
       <c r="X315" s="1"/>
@@ -29687,7 +29718,7 @@
       <c r="R316" s="1"/>
       <c r="S316" s="1"/>
       <c r="T316" s="1"/>
-      <c r="U316" s="1"/>
+      <c r="U316" s="20"/>
       <c r="V316" s="1"/>
       <c r="W316" s="1"/>
       <c r="X316" s="1"/>
@@ -29742,7 +29773,7 @@
       <c r="R317" s="1"/>
       <c r="S317" s="1"/>
       <c r="T317" s="1"/>
-      <c r="U317" s="1"/>
+      <c r="U317" s="20"/>
       <c r="V317" s="1"/>
       <c r="W317" s="1"/>
       <c r="X317" s="1"/>
@@ -29797,7 +29828,7 @@
       <c r="R318" s="1"/>
       <c r="S318" s="1"/>
       <c r="T318" s="1"/>
-      <c r="U318" s="1"/>
+      <c r="U318" s="20"/>
       <c r="V318" s="1"/>
       <c r="W318" s="1"/>
       <c r="X318" s="1"/>
@@ -29852,7 +29883,7 @@
       <c r="R319" s="1"/>
       <c r="S319" s="1"/>
       <c r="T319" s="1"/>
-      <c r="U319" s="1"/>
+      <c r="U319" s="20"/>
       <c r="V319" s="1"/>
       <c r="W319" s="1"/>
       <c r="X319" s="1"/>
@@ -29907,7 +29938,7 @@
       <c r="R320" s="1"/>
       <c r="S320" s="1"/>
       <c r="T320" s="1"/>
-      <c r="U320" s="1"/>
+      <c r="U320" s="20"/>
       <c r="V320" s="1"/>
       <c r="W320" s="1"/>
       <c r="X320" s="1"/>
@@ -29962,7 +29993,7 @@
       <c r="R321" s="1"/>
       <c r="S321" s="1"/>
       <c r="T321" s="1"/>
-      <c r="U321" s="1"/>
+      <c r="U321" s="20"/>
       <c r="V321" s="1"/>
       <c r="W321" s="1"/>
       <c r="X321" s="1"/>
@@ -30017,7 +30048,7 @@
       <c r="R322" s="1"/>
       <c r="S322" s="1"/>
       <c r="T322" s="1"/>
-      <c r="U322" s="1"/>
+      <c r="U322" s="20"/>
       <c r="V322" s="1"/>
       <c r="W322" s="1"/>
       <c r="X322" s="1"/>
@@ -30072,7 +30103,7 @@
       <c r="R323" s="1"/>
       <c r="S323" s="1"/>
       <c r="T323" s="1"/>
-      <c r="U323" s="1"/>
+      <c r="U323" s="20"/>
       <c r="V323" s="1"/>
       <c r="W323" s="1"/>
       <c r="X323" s="1"/>
@@ -30127,7 +30158,7 @@
       <c r="R324" s="1"/>
       <c r="S324" s="1"/>
       <c r="T324" s="1"/>
-      <c r="U324" s="1"/>
+      <c r="U324" s="20"/>
       <c r="V324" s="1"/>
       <c r="W324" s="1"/>
       <c r="X324" s="1"/>
@@ -30182,7 +30213,7 @@
       <c r="R325" s="1"/>
       <c r="S325" s="1"/>
       <c r="T325" s="1"/>
-      <c r="U325" s="1"/>
+      <c r="U325" s="20"/>
       <c r="V325" s="1"/>
       <c r="W325" s="1"/>
       <c r="X325" s="1"/>
@@ -30237,7 +30268,7 @@
       <c r="R326" s="1"/>
       <c r="S326" s="1"/>
       <c r="T326" s="1"/>
-      <c r="U326" s="1"/>
+      <c r="U326" s="20"/>
       <c r="V326" s="1"/>
       <c r="W326" s="1"/>
       <c r="X326" s="1"/>
@@ -30292,7 +30323,7 @@
       <c r="R327" s="1"/>
       <c r="S327" s="1"/>
       <c r="T327" s="1"/>
-      <c r="U327" s="1"/>
+      <c r="U327" s="20"/>
       <c r="V327" s="1"/>
       <c r="W327" s="1"/>
       <c r="X327" s="1"/>
@@ -30347,7 +30378,7 @@
       <c r="R328" s="1"/>
       <c r="S328" s="1"/>
       <c r="T328" s="1"/>
-      <c r="U328" s="1"/>
+      <c r="U328" s="20"/>
       <c r="V328" s="1"/>
       <c r="W328" s="1"/>
       <c r="X328" s="1"/>
@@ -30402,7 +30433,7 @@
       <c r="R329" s="1"/>
       <c r="S329" s="1"/>
       <c r="T329" s="1"/>
-      <c r="U329" s="1"/>
+      <c r="U329" s="20"/>
       <c r="V329" s="1"/>
       <c r="W329" s="1"/>
       <c r="X329" s="1"/>
@@ -30457,7 +30488,7 @@
       <c r="R330" s="1"/>
       <c r="S330" s="1"/>
       <c r="T330" s="1"/>
-      <c r="U330" s="1"/>
+      <c r="U330" s="20"/>
       <c r="V330" s="1"/>
       <c r="W330" s="1"/>
       <c r="X330" s="1"/>
@@ -30512,7 +30543,7 @@
       <c r="R331" s="1"/>
       <c r="S331" s="1"/>
       <c r="T331" s="1"/>
-      <c r="U331" s="1"/>
+      <c r="U331" s="20"/>
       <c r="V331" s="1"/>
       <c r="W331" s="1"/>
       <c r="X331" s="1"/>
@@ -30567,7 +30598,7 @@
       <c r="R332" s="1"/>
       <c r="S332" s="1"/>
       <c r="T332" s="1"/>
-      <c r="U332" s="1"/>
+      <c r="U332" s="20"/>
       <c r="V332" s="1"/>
       <c r="W332" s="1"/>
       <c r="X332" s="1"/>
@@ -30622,7 +30653,7 @@
       <c r="R333" s="1"/>
       <c r="S333" s="1"/>
       <c r="T333" s="1"/>
-      <c r="U333" s="1"/>
+      <c r="U333" s="20"/>
       <c r="V333" s="1"/>
       <c r="W333" s="1"/>
       <c r="X333" s="1"/>
@@ -30677,7 +30708,7 @@
       <c r="R334" s="1"/>
       <c r="S334" s="1"/>
       <c r="T334" s="1"/>
-      <c r="U334" s="1"/>
+      <c r="U334" s="20"/>
       <c r="V334" s="1"/>
       <c r="W334" s="1"/>
       <c r="X334" s="1"/>
@@ -30732,7 +30763,7 @@
       <c r="R335" s="1"/>
       <c r="S335" s="1"/>
       <c r="T335" s="1"/>
-      <c r="U335" s="1"/>
+      <c r="U335" s="20"/>
       <c r="V335" s="1"/>
       <c r="W335" s="1"/>
       <c r="X335" s="1"/>
@@ -30787,7 +30818,7 @@
       <c r="R336" s="1"/>
       <c r="S336" s="1"/>
       <c r="T336" s="1"/>
-      <c r="U336" s="1"/>
+      <c r="U336" s="20"/>
       <c r="V336" s="1"/>
       <c r="W336" s="1"/>
       <c r="X336" s="1"/>
@@ -30842,7 +30873,7 @@
       <c r="R337" s="1"/>
       <c r="S337" s="1"/>
       <c r="T337" s="1"/>
-      <c r="U337" s="1"/>
+      <c r="U337" s="20"/>
       <c r="V337" s="1"/>
       <c r="W337" s="1"/>
       <c r="X337" s="1"/>
@@ -30897,7 +30928,7 @@
       <c r="R338" s="1"/>
       <c r="S338" s="1"/>
       <c r="T338" s="1"/>
-      <c r="U338" s="1"/>
+      <c r="U338" s="20"/>
       <c r="V338" s="1"/>
       <c r="W338" s="1"/>
       <c r="X338" s="1"/>
@@ -30952,7 +30983,7 @@
       <c r="R339" s="1"/>
       <c r="S339" s="1"/>
       <c r="T339" s="1"/>
-      <c r="U339" s="1"/>
+      <c r="U339" s="20"/>
       <c r="V339" s="1"/>
       <c r="W339" s="1"/>
       <c r="X339" s="1"/>
@@ -31007,7 +31038,7 @@
       <c r="R340" s="1"/>
       <c r="S340" s="1"/>
       <c r="T340" s="1"/>
-      <c r="U340" s="1"/>
+      <c r="U340" s="20"/>
       <c r="V340" s="1"/>
       <c r="W340" s="1"/>
       <c r="X340" s="1"/>
@@ -31062,7 +31093,7 @@
       <c r="R341" s="1"/>
       <c r="S341" s="1"/>
       <c r="T341" s="1"/>
-      <c r="U341" s="1"/>
+      <c r="U341" s="20"/>
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
       <c r="X341" s="1"/>
@@ -31117,7 +31148,7 @@
       <c r="R342" s="1"/>
       <c r="S342" s="1"/>
       <c r="T342" s="1"/>
-      <c r="U342" s="1"/>
+      <c r="U342" s="20"/>
       <c r="V342" s="1"/>
       <c r="W342" s="1"/>
       <c r="X342" s="1"/>
@@ -31172,7 +31203,7 @@
       <c r="R343" s="1"/>
       <c r="S343" s="1"/>
       <c r="T343" s="1"/>
-      <c r="U343" s="1"/>
+      <c r="U343" s="20"/>
       <c r="V343" s="1"/>
       <c r="W343" s="1"/>
       <c r="X343" s="1"/>
@@ -31227,7 +31258,7 @@
       <c r="R344" s="1"/>
       <c r="S344" s="1"/>
       <c r="T344" s="1"/>
-      <c r="U344" s="1"/>
+      <c r="U344" s="20"/>
       <c r="V344" s="1"/>
       <c r="W344" s="1"/>
       <c r="X344" s="1"/>
@@ -31282,7 +31313,7 @@
       <c r="R345" s="1"/>
       <c r="S345" s="1"/>
       <c r="T345" s="1"/>
-      <c r="U345" s="1"/>
+      <c r="U345" s="20"/>
       <c r="V345" s="1"/>
       <c r="W345" s="1"/>
       <c r="X345" s="1"/>
@@ -31337,7 +31368,7 @@
       <c r="R346" s="1"/>
       <c r="S346" s="1"/>
       <c r="T346" s="1"/>
-      <c r="U346" s="1"/>
+      <c r="U346" s="20"/>
       <c r="V346" s="1"/>
       <c r="W346" s="1"/>
       <c r="X346" s="1"/>
@@ -31392,7 +31423,7 @@
       <c r="R347" s="1"/>
       <c r="S347" s="1"/>
       <c r="T347" s="1"/>
-      <c r="U347" s="1"/>
+      <c r="U347" s="20"/>
       <c r="V347" s="1"/>
       <c r="W347" s="1"/>
       <c r="X347" s="1"/>
@@ -31447,7 +31478,7 @@
       <c r="R348" s="1"/>
       <c r="S348" s="1"/>
       <c r="T348" s="1"/>
-      <c r="U348" s="1"/>
+      <c r="U348" s="20"/>
       <c r="V348" s="1"/>
       <c r="W348" s="1"/>
       <c r="X348" s="1"/>
@@ -31502,7 +31533,7 @@
       <c r="R349" s="1"/>
       <c r="S349" s="1"/>
       <c r="T349" s="1"/>
-      <c r="U349" s="1"/>
+      <c r="U349" s="20"/>
       <c r="V349" s="1"/>
       <c r="W349" s="1"/>
       <c r="X349" s="1"/>
@@ -31557,7 +31588,7 @@
       <c r="R350" s="1"/>
       <c r="S350" s="1"/>
       <c r="T350" s="1"/>
-      <c r="U350" s="1"/>
+      <c r="U350" s="20"/>
       <c r="V350" s="1"/>
       <c r="W350" s="1"/>
       <c r="X350" s="1"/>
@@ -31612,7 +31643,7 @@
       <c r="R351" s="1"/>
       <c r="S351" s="1"/>
       <c r="T351" s="1"/>
-      <c r="U351" s="1"/>
+      <c r="U351" s="20"/>
       <c r="V351" s="1"/>
       <c r="W351" s="1"/>
       <c r="X351" s="1"/>
@@ -31667,7 +31698,7 @@
       <c r="R352" s="1"/>
       <c r="S352" s="1"/>
       <c r="T352" s="1"/>
-      <c r="U352" s="1"/>
+      <c r="U352" s="20"/>
       <c r="V352" s="1"/>
       <c r="W352" s="1"/>
       <c r="X352" s="1"/>
@@ -31722,7 +31753,7 @@
       <c r="R353" s="1"/>
       <c r="S353" s="1"/>
       <c r="T353" s="1"/>
-      <c r="U353" s="1"/>
+      <c r="U353" s="20"/>
       <c r="V353" s="1"/>
       <c r="W353" s="1"/>
       <c r="X353" s="1"/>
@@ -31777,7 +31808,7 @@
       <c r="R354" s="1"/>
       <c r="S354" s="1"/>
       <c r="T354" s="1"/>
-      <c r="U354" s="1"/>
+      <c r="U354" s="20"/>
       <c r="V354" s="1"/>
       <c r="W354" s="1"/>
       <c r="X354" s="1"/>
@@ -31832,7 +31863,7 @@
       <c r="R355" s="1"/>
       <c r="S355" s="1"/>
       <c r="T355" s="1"/>
-      <c r="U355" s="1"/>
+      <c r="U355" s="20"/>
       <c r="V355" s="1"/>
       <c r="W355" s="1"/>
       <c r="X355" s="1"/>
@@ -31887,7 +31918,7 @@
       <c r="R356" s="1"/>
       <c r="S356" s="1"/>
       <c r="T356" s="1"/>
-      <c r="U356" s="1"/>
+      <c r="U356" s="20"/>
       <c r="V356" s="1"/>
       <c r="W356" s="1"/>
       <c r="X356" s="1"/>
@@ -31942,7 +31973,7 @@
       <c r="R357" s="1"/>
       <c r="S357" s="1"/>
       <c r="T357" s="1"/>
-      <c r="U357" s="1"/>
+      <c r="U357" s="20"/>
       <c r="V357" s="1"/>
       <c r="W357" s="1"/>
       <c r="X357" s="1"/>
@@ -31997,7 +32028,7 @@
       <c r="R358" s="1"/>
       <c r="S358" s="1"/>
       <c r="T358" s="1"/>
-      <c r="U358" s="1"/>
+      <c r="U358" s="20"/>
       <c r="V358" s="1"/>
       <c r="W358" s="1"/>
       <c r="X358" s="1"/>
@@ -32052,7 +32083,7 @@
       <c r="R359" s="1"/>
       <c r="S359" s="1"/>
       <c r="T359" s="1"/>
-      <c r="U359" s="1"/>
+      <c r="U359" s="20"/>
       <c r="V359" s="1"/>
       <c r="W359" s="1"/>
       <c r="X359" s="1"/>
@@ -32107,7 +32138,7 @@
       <c r="R360" s="1"/>
       <c r="S360" s="1"/>
       <c r="T360" s="1"/>
-      <c r="U360" s="1"/>
+      <c r="U360" s="20"/>
       <c r="V360" s="1"/>
       <c r="W360" s="1"/>
       <c r="X360" s="1"/>
@@ -32162,7 +32193,7 @@
       <c r="R361" s="1"/>
       <c r="S361" s="1"/>
       <c r="T361" s="1"/>
-      <c r="U361" s="1"/>
+      <c r="U361" s="20"/>
       <c r="V361" s="1"/>
       <c r="W361" s="1"/>
       <c r="X361" s="1"/>
@@ -32217,7 +32248,7 @@
       <c r="R362" s="1"/>
       <c r="S362" s="1"/>
       <c r="T362" s="1"/>
-      <c r="U362" s="1"/>
+      <c r="U362" s="20"/>
       <c r="V362" s="1"/>
       <c r="W362" s="1"/>
       <c r="X362" s="1"/>
@@ -32272,7 +32303,7 @@
       <c r="R363" s="1"/>
       <c r="S363" s="1"/>
       <c r="T363" s="1"/>
-      <c r="U363" s="1"/>
+      <c r="U363" s="20"/>
       <c r="V363" s="1"/>
       <c r="W363" s="1"/>
       <c r="X363" s="1"/>
@@ -32327,7 +32358,7 @@
       <c r="R364" s="1"/>
       <c r="S364" s="1"/>
       <c r="T364" s="1"/>
-      <c r="U364" s="1"/>
+      <c r="U364" s="20"/>
       <c r="V364" s="1"/>
       <c r="W364" s="1"/>
       <c r="X364" s="1"/>
@@ -32382,7 +32413,7 @@
       <c r="R365" s="1"/>
       <c r="S365" s="1"/>
       <c r="T365" s="1"/>
-      <c r="U365" s="1"/>
+      <c r="U365" s="20"/>
       <c r="V365" s="1"/>
       <c r="W365" s="1"/>
       <c r="X365" s="1"/>
@@ -32437,7 +32468,7 @@
       <c r="R366" s="1"/>
       <c r="S366" s="1"/>
       <c r="T366" s="1"/>
-      <c r="U366" s="1"/>
+      <c r="U366" s="20"/>
       <c r="V366" s="1"/>
       <c r="W366" s="1"/>
       <c r="X366" s="1"/>
@@ -32492,7 +32523,7 @@
       <c r="R367" s="1"/>
       <c r="S367" s="1"/>
       <c r="T367" s="1"/>
-      <c r="U367" s="1"/>
+      <c r="U367" s="20"/>
       <c r="V367" s="1"/>
       <c r="W367" s="1"/>
       <c r="X367" s="1"/>
@@ -32547,7 +32578,7 @@
       <c r="R368" s="1"/>
       <c r="S368" s="1"/>
       <c r="T368" s="1"/>
-      <c r="U368" s="1"/>
+      <c r="U368" s="20"/>
       <c r="V368" s="1"/>
       <c r="W368" s="1"/>
       <c r="X368" s="1"/>
@@ -32602,7 +32633,7 @@
       <c r="R369" s="1"/>
       <c r="S369" s="1"/>
       <c r="T369" s="1"/>
-      <c r="U369" s="1"/>
+      <c r="U369" s="20"/>
       <c r="V369" s="1"/>
       <c r="W369" s="1"/>
       <c r="X369" s="1"/>
@@ -32657,7 +32688,7 @@
       <c r="R370" s="1"/>
       <c r="S370" s="1"/>
       <c r="T370" s="1"/>
-      <c r="U370" s="1"/>
+      <c r="U370" s="20"/>
       <c r="V370" s="1"/>
       <c r="W370" s="1"/>
       <c r="X370" s="1"/>
@@ -32712,7 +32743,7 @@
       <c r="R371" s="1"/>
       <c r="S371" s="1"/>
       <c r="T371" s="1"/>
-      <c r="U371" s="1"/>
+      <c r="U371" s="20"/>
       <c r="V371" s="1"/>
       <c r="W371" s="1"/>
       <c r="X371" s="1"/>
@@ -32767,7 +32798,7 @@
       <c r="R372" s="1"/>
       <c r="S372" s="1"/>
       <c r="T372" s="1"/>
-      <c r="U372" s="1"/>
+      <c r="U372" s="20"/>
       <c r="V372" s="1"/>
       <c r="W372" s="1"/>
       <c r="X372" s="1"/>
@@ -32822,7 +32853,7 @@
       <c r="R373" s="1"/>
       <c r="S373" s="1"/>
       <c r="T373" s="1"/>
-      <c r="U373" s="1"/>
+      <c r="U373" s="20"/>
       <c r="V373" s="1"/>
       <c r="W373" s="1"/>
       <c r="X373" s="1"/>
@@ -32877,7 +32908,7 @@
       <c r="R374" s="1"/>
       <c r="S374" s="1"/>
       <c r="T374" s="1"/>
-      <c r="U374" s="1"/>
+      <c r="U374" s="20"/>
       <c r="V374" s="1"/>
       <c r="W374" s="1"/>
       <c r="X374" s="1"/>
@@ -32932,7 +32963,7 @@
       <c r="R375" s="1"/>
       <c r="S375" s="1"/>
       <c r="T375" s="1"/>
-      <c r="U375" s="1"/>
+      <c r="U375" s="20"/>
       <c r="V375" s="1"/>
       <c r="W375" s="1"/>
       <c r="X375" s="1"/>
@@ -32987,7 +33018,7 @@
       <c r="R376" s="1"/>
       <c r="S376" s="1"/>
       <c r="T376" s="1"/>
-      <c r="U376" s="1"/>
+      <c r="U376" s="20"/>
       <c r="V376" s="1"/>
       <c r="W376" s="1"/>
       <c r="X376" s="1"/>
@@ -33042,7 +33073,7 @@
       <c r="R377" s="1"/>
       <c r="S377" s="1"/>
       <c r="T377" s="1"/>
-      <c r="U377" s="1"/>
+      <c r="U377" s="20"/>
       <c r="V377" s="1"/>
       <c r="W377" s="1"/>
       <c r="X377" s="1"/>
@@ -33097,7 +33128,7 @@
       <c r="R378" s="1"/>
       <c r="S378" s="1"/>
       <c r="T378" s="1"/>
-      <c r="U378" s="1"/>
+      <c r="U378" s="20"/>
       <c r="V378" s="1"/>
       <c r="W378" s="1"/>
       <c r="X378" s="1"/>
@@ -33152,7 +33183,7 @@
       <c r="R379" s="1"/>
       <c r="S379" s="1"/>
       <c r="T379" s="1"/>
-      <c r="U379" s="1"/>
+      <c r="U379" s="20"/>
       <c r="V379" s="1"/>
       <c r="W379" s="1"/>
       <c r="X379" s="1"/>
@@ -33207,7 +33238,7 @@
       <c r="R380" s="1"/>
       <c r="S380" s="1"/>
       <c r="T380" s="1"/>
-      <c r="U380" s="1"/>
+      <c r="U380" s="20"/>
       <c r="V380" s="1"/>
       <c r="W380" s="1"/>
       <c r="X380" s="1"/>
@@ -33262,7 +33293,7 @@
       <c r="R381" s="1"/>
       <c r="S381" s="1"/>
       <c r="T381" s="1"/>
-      <c r="U381" s="1"/>
+      <c r="U381" s="20"/>
       <c r="V381" s="1"/>
       <c r="W381" s="1"/>
       <c r="X381" s="1"/>
@@ -33317,7 +33348,7 @@
       <c r="R382" s="1"/>
       <c r="S382" s="1"/>
       <c r="T382" s="1"/>
-      <c r="U382" s="1"/>
+      <c r="U382" s="20"/>
       <c r="V382" s="1"/>
       <c r="W382" s="1"/>
       <c r="X382" s="1"/>
@@ -33372,7 +33403,7 @@
       <c r="R383" s="1"/>
       <c r="S383" s="1"/>
       <c r="T383" s="1"/>
-      <c r="U383" s="1"/>
+      <c r="U383" s="20"/>
       <c r="V383" s="1"/>
       <c r="W383" s="1"/>
       <c r="X383" s="1"/>
@@ -33427,7 +33458,7 @@
       <c r="R384" s="1"/>
       <c r="S384" s="1"/>
       <c r="T384" s="1"/>
-      <c r="U384" s="1"/>
+      <c r="U384" s="20"/>
       <c r="V384" s="1"/>
       <c r="W384" s="1"/>
       <c r="X384" s="1"/>
@@ -33482,7 +33513,7 @@
       <c r="R385" s="1"/>
       <c r="S385" s="1"/>
       <c r="T385" s="1"/>
-      <c r="U385" s="1"/>
+      <c r="U385" s="20"/>
       <c r="V385" s="1"/>
       <c r="W385" s="1"/>
       <c r="X385" s="1"/>
@@ -33537,7 +33568,7 @@
       <c r="R386" s="1"/>
       <c r="S386" s="1"/>
       <c r="T386" s="1"/>
-      <c r="U386" s="1"/>
+      <c r="U386" s="20"/>
       <c r="V386" s="1"/>
       <c r="W386" s="1"/>
       <c r="X386" s="1"/>
@@ -33592,7 +33623,7 @@
       <c r="R387" s="1"/>
       <c r="S387" s="1"/>
       <c r="T387" s="1"/>
-      <c r="U387" s="1"/>
+      <c r="U387" s="20"/>
       <c r="V387" s="1"/>
       <c r="W387" s="1"/>
       <c r="X387" s="1"/>
@@ -33647,7 +33678,7 @@
       <c r="R388" s="1"/>
       <c r="S388" s="1"/>
       <c r="T388" s="1"/>
-      <c r="U388" s="1"/>
+      <c r="U388" s="20"/>
       <c r="V388" s="1"/>
       <c r="W388" s="1"/>
       <c r="X388" s="1"/>
@@ -33702,7 +33733,7 @@
       <c r="R389" s="1"/>
       <c r="S389" s="1"/>
       <c r="T389" s="1"/>
-      <c r="U389" s="1"/>
+      <c r="U389" s="20"/>
       <c r="V389" s="1"/>
       <c r="W389" s="1"/>
       <c r="X389" s="1"/>
@@ -33757,7 +33788,7 @@
       <c r="R390" s="1"/>
       <c r="S390" s="1"/>
       <c r="T390" s="1"/>
-      <c r="U390" s="1"/>
+      <c r="U390" s="20"/>
       <c r="V390" s="1"/>
       <c r="W390" s="1"/>
       <c r="X390" s="1"/>
@@ -33812,7 +33843,7 @@
       <c r="R391" s="1"/>
       <c r="S391" s="1"/>
       <c r="T391" s="1"/>
-      <c r="U391" s="1"/>
+      <c r="U391" s="20"/>
       <c r="V391" s="1"/>
       <c r="W391" s="1"/>
       <c r="X391" s="1"/>
@@ -33867,7 +33898,7 @@
       <c r="R392" s="1"/>
       <c r="S392" s="1"/>
       <c r="T392" s="1"/>
-      <c r="U392" s="1"/>
+      <c r="U392" s="20"/>
       <c r="V392" s="1"/>
       <c r="W392" s="1"/>
       <c r="X392" s="1"/>
@@ -33922,7 +33953,7 @@
       <c r="R393" s="1"/>
       <c r="S393" s="1"/>
       <c r="T393" s="1"/>
-      <c r="U393" s="1"/>
+      <c r="U393" s="20"/>
       <c r="V393" s="1"/>
       <c r="W393" s="1"/>
       <c r="X393" s="1"/>
@@ -33977,7 +34008,7 @@
       <c r="R394" s="1"/>
       <c r="S394" s="1"/>
       <c r="T394" s="1"/>
-      <c r="U394" s="1"/>
+      <c r="U394" s="20"/>
       <c r="V394" s="1"/>
       <c r="W394" s="1"/>
       <c r="X394" s="1"/>
@@ -34032,7 +34063,7 @@
       <c r="R395" s="1"/>
       <c r="S395" s="1"/>
       <c r="T395" s="1"/>
-      <c r="U395" s="1"/>
+      <c r="U395" s="20"/>
       <c r="V395" s="1"/>
       <c r="W395" s="1"/>
       <c r="X395" s="1"/>
@@ -34087,7 +34118,7 @@
       <c r="R396" s="1"/>
       <c r="S396" s="1"/>
       <c r="T396" s="1"/>
-      <c r="U396" s="1"/>
+      <c r="U396" s="20"/>
       <c r="V396" s="1"/>
       <c r="W396" s="1"/>
       <c r="X396" s="1"/>
@@ -34142,7 +34173,7 @@
       <c r="R397" s="1"/>
       <c r="S397" s="1"/>
       <c r="T397" s="1"/>
-      <c r="U397" s="1"/>
+      <c r="U397" s="20"/>
       <c r="V397" s="1"/>
       <c r="W397" s="1"/>
       <c r="X397" s="1"/>
@@ -34197,7 +34228,7 @@
       <c r="R398" s="1"/>
       <c r="S398" s="1"/>
       <c r="T398" s="1"/>
-      <c r="U398" s="1"/>
+      <c r="U398" s="20"/>
       <c r="V398" s="1"/>
       <c r="W398" s="1"/>
       <c r="X398" s="1"/>
@@ -34252,7 +34283,7 @@
       <c r="R399" s="1"/>
       <c r="S399" s="1"/>
       <c r="T399" s="1"/>
-      <c r="U399" s="1"/>
+      <c r="U399" s="20"/>
       <c r="V399" s="1"/>
       <c r="W399" s="1"/>
       <c r="X399" s="1"/>
@@ -34307,7 +34338,7 @@
       <c r="R400" s="1"/>
       <c r="S400" s="1"/>
       <c r="T400" s="1"/>
-      <c r="U400" s="1"/>
+      <c r="U400" s="20"/>
       <c r="V400" s="1"/>
       <c r="W400" s="1"/>
       <c r="X400" s="1"/>
@@ -34362,7 +34393,7 @@
       <c r="R401" s="1"/>
       <c r="S401" s="1"/>
       <c r="T401" s="1"/>
-      <c r="U401" s="1"/>
+      <c r="U401" s="20"/>
       <c r="V401" s="1"/>
       <c r="W401" s="1"/>
       <c r="X401" s="1"/>
@@ -34417,7 +34448,7 @@
       <c r="R402" s="1"/>
       <c r="S402" s="1"/>
       <c r="T402" s="1"/>
-      <c r="U402" s="1"/>
+      <c r="U402" s="20"/>
       <c r="V402" s="1"/>
       <c r="W402" s="1"/>
       <c r="X402" s="1"/>
@@ -34472,7 +34503,7 @@
       <c r="R403" s="1"/>
       <c r="S403" s="1"/>
       <c r="T403" s="1"/>
-      <c r="U403" s="1"/>
+      <c r="U403" s="20"/>
       <c r="V403" s="1"/>
       <c r="W403" s="1"/>
       <c r="X403" s="1"/>
@@ -34527,7 +34558,7 @@
       <c r="R404" s="1"/>
       <c r="S404" s="1"/>
       <c r="T404" s="1"/>
-      <c r="U404" s="1"/>
+      <c r="U404" s="20"/>
       <c r="V404" s="1"/>
       <c r="W404" s="1"/>
       <c r="X404" s="1"/>
@@ -34582,7 +34613,7 @@
       <c r="R405" s="1"/>
       <c r="S405" s="1"/>
       <c r="T405" s="1"/>
-      <c r="U405" s="1"/>
+      <c r="U405" s="20"/>
       <c r="V405" s="1"/>
       <c r="W405" s="1"/>
       <c r="X405" s="1"/>
@@ -34637,7 +34668,7 @@
       <c r="R406" s="1"/>
       <c r="S406" s="1"/>
       <c r="T406" s="1"/>
-      <c r="U406" s="1"/>
+      <c r="U406" s="20"/>
       <c r="V406" s="1"/>
       <c r="W406" s="1"/>
       <c r="X406" s="1"/>
@@ -34692,7 +34723,7 @@
       <c r="R407" s="1"/>
       <c r="S407" s="1"/>
       <c r="T407" s="1"/>
-      <c r="U407" s="1"/>
+      <c r="U407" s="20"/>
       <c r="V407" s="1"/>
       <c r="W407" s="1"/>
       <c r="X407" s="1"/>
@@ -34747,7 +34778,7 @@
       <c r="R408" s="1"/>
       <c r="S408" s="1"/>
       <c r="T408" s="1"/>
-      <c r="U408" s="1"/>
+      <c r="U408" s="20"/>
       <c r="V408" s="1"/>
       <c r="W408" s="1"/>
       <c r="X408" s="1"/>
@@ -34802,7 +34833,7 @@
       <c r="R409" s="1"/>
       <c r="S409" s="1"/>
       <c r="T409" s="1"/>
-      <c r="U409" s="1"/>
+      <c r="U409" s="20"/>
       <c r="V409" s="1"/>
       <c r="W409" s="1"/>
       <c r="X409" s="1"/>
@@ -34857,7 +34888,7 @@
       <c r="R410" s="1"/>
       <c r="S410" s="1"/>
       <c r="T410" s="1"/>
-      <c r="U410" s="1"/>
+      <c r="U410" s="20"/>
       <c r="V410" s="1"/>
       <c r="W410" s="1"/>
       <c r="X410" s="1"/>
@@ -34912,7 +34943,7 @@
       <c r="R411" s="1"/>
       <c r="S411" s="1"/>
       <c r="T411" s="1"/>
-      <c r="U411" s="1"/>
+      <c r="U411" s="20"/>
       <c r="V411" s="1"/>
       <c r="W411" s="1"/>
       <c r="X411" s="1"/>
@@ -34967,7 +34998,7 @@
       <c r="R412" s="1"/>
       <c r="S412" s="1"/>
       <c r="T412" s="1"/>
-      <c r="U412" s="1"/>
+      <c r="U412" s="20"/>
       <c r="V412" s="1"/>
       <c r="W412" s="1"/>
       <c r="X412" s="1"/>
@@ -35022,7 +35053,7 @@
       <c r="R413" s="1"/>
       <c r="S413" s="1"/>
       <c r="T413" s="1"/>
-      <c r="U413" s="1"/>
+      <c r="U413" s="20"/>
       <c r="V413" s="1"/>
       <c r="W413" s="1"/>
       <c r="X413" s="1"/>
@@ -35077,7 +35108,7 @@
       <c r="R414" s="1"/>
       <c r="S414" s="1"/>
       <c r="T414" s="1"/>
-      <c r="U414" s="1"/>
+      <c r="U414" s="20"/>
       <c r="V414" s="1"/>
       <c r="W414" s="1"/>
       <c r="X414" s="1"/>
@@ -35132,7 +35163,7 @@
       <c r="R415" s="1"/>
       <c r="S415" s="1"/>
       <c r="T415" s="1"/>
-      <c r="U415" s="1"/>
+      <c r="U415" s="20"/>
       <c r="V415" s="1"/>
       <c r="W415" s="1"/>
       <c r="X415" s="1"/>
@@ -35187,7 +35218,7 @@
       <c r="R416" s="1"/>
       <c r="S416" s="1"/>
       <c r="T416" s="1"/>
-      <c r="U416" s="1"/>
+      <c r="U416" s="20"/>
       <c r="V416" s="1"/>
       <c r="W416" s="1"/>
       <c r="X416" s="1"/>
@@ -35242,7 +35273,7 @@
       <c r="R417" s="1"/>
       <c r="S417" s="1"/>
       <c r="T417" s="1"/>
-      <c r="U417" s="1"/>
+      <c r="U417" s="20"/>
       <c r="V417" s="1"/>
       <c r="W417" s="1"/>
       <c r="X417" s="1"/>
@@ -35297,7 +35328,7 @@
       <c r="R418" s="1"/>
       <c r="S418" s="1"/>
       <c r="T418" s="1"/>
-      <c r="U418" s="1"/>
+      <c r="U418" s="20"/>
       <c r="V418" s="1"/>
       <c r="W418" s="1"/>
       <c r="X418" s="1"/>
@@ -35352,7 +35383,7 @@
       <c r="R419" s="1"/>
       <c r="S419" s="1"/>
       <c r="T419" s="1"/>
-      <c r="U419" s="1"/>
+      <c r="U419" s="20"/>
       <c r="V419" s="1"/>
       <c r="W419" s="1"/>
       <c r="X419" s="1"/>
@@ -35407,7 +35438,7 @@
       <c r="R420" s="1"/>
       <c r="S420" s="1"/>
       <c r="T420" s="1"/>
-      <c r="U420" s="1"/>
+      <c r="U420" s="20"/>
       <c r="V420" s="1"/>
       <c r="W420" s="1"/>
       <c r="X420" s="1"/>
@@ -35462,7 +35493,7 @@
       <c r="R421" s="1"/>
       <c r="S421" s="1"/>
       <c r="T421" s="1"/>
-      <c r="U421" s="1"/>
+      <c r="U421" s="20"/>
       <c r="V421" s="1"/>
       <c r="W421" s="1"/>
       <c r="X421" s="1"/>
@@ -35517,7 +35548,7 @@
       <c r="R422" s="1"/>
       <c r="S422" s="1"/>
       <c r="T422" s="1"/>
-      <c r="U422" s="1"/>
+      <c r="U422" s="20"/>
       <c r="V422" s="1"/>
       <c r="W422" s="1"/>
       <c r="X422" s="1"/>
@@ -35572,7 +35603,7 @@
       <c r="R423" s="1"/>
       <c r="S423" s="1"/>
       <c r="T423" s="1"/>
-      <c r="U423" s="1"/>
+      <c r="U423" s="20"/>
       <c r="V423" s="1"/>
       <c r="W423" s="1"/>
       <c r="X423" s="1"/>
@@ -35627,7 +35658,7 @@
       <c r="R424" s="1"/>
       <c r="S424" s="1"/>
       <c r="T424" s="1"/>
-      <c r="U424" s="1"/>
+      <c r="U424" s="20"/>
       <c r="V424" s="1"/>
       <c r="W424" s="1"/>
       <c r="X424" s="1"/>
@@ -35682,7 +35713,7 @@
       <c r="R425" s="1"/>
       <c r="S425" s="1"/>
       <c r="T425" s="1"/>
-      <c r="U425" s="1"/>
+      <c r="U425" s="20"/>
       <c r="V425" s="1"/>
       <c r="W425" s="1"/>
       <c r="X425" s="1"/>
@@ -35737,7 +35768,7 @@
       <c r="R426" s="1"/>
       <c r="S426" s="1"/>
       <c r="T426" s="1"/>
-      <c r="U426" s="1"/>
+      <c r="U426" s="20"/>
       <c r="V426" s="1"/>
       <c r="W426" s="1"/>
       <c r="X426" s="1"/>
@@ -35792,7 +35823,7 @@
       <c r="R427" s="1"/>
       <c r="S427" s="1"/>
       <c r="T427" s="1"/>
-      <c r="U427" s="1"/>
+      <c r="U427" s="20"/>
       <c r="V427" s="1"/>
       <c r="W427" s="1"/>
       <c r="X427" s="1"/>
@@ -35847,7 +35878,7 @@
       <c r="R428" s="1"/>
       <c r="S428" s="1"/>
       <c r="T428" s="1"/>
-      <c r="U428" s="1"/>
+      <c r="U428" s="20"/>
       <c r="V428" s="1"/>
       <c r="W428" s="1"/>
       <c r="X428" s="1"/>
@@ -35902,7 +35933,7 @@
       <c r="R429" s="1"/>
       <c r="S429" s="1"/>
       <c r="T429" s="1"/>
-      <c r="U429" s="1"/>
+      <c r="U429" s="20"/>
       <c r="V429" s="1"/>
       <c r="W429" s="1"/>
       <c r="X429" s="1"/>
@@ -35957,7 +35988,7 @@
       <c r="R430" s="1"/>
       <c r="S430" s="1"/>
       <c r="T430" s="1"/>
-      <c r="U430" s="1"/>
+      <c r="U430" s="20"/>
       <c r="V430" s="1"/>
       <c r="W430" s="1"/>
       <c r="X430" s="1"/>
@@ -36012,7 +36043,7 @@
       <c r="R431" s="1"/>
       <c r="S431" s="1"/>
       <c r="T431" s="1"/>
-      <c r="U431" s="1"/>
+      <c r="U431" s="20"/>
       <c r="V431" s="1"/>
       <c r="W431" s="1"/>
       <c r="X431" s="1"/>
@@ -36067,7 +36098,7 @@
       <c r="R432" s="1"/>
       <c r="S432" s="1"/>
       <c r="T432" s="1"/>
-      <c r="U432" s="1"/>
+      <c r="U432" s="20"/>
       <c r="V432" s="1"/>
       <c r="W432" s="1"/>
       <c r="X432" s="1"/>
@@ -36122,7 +36153,7 @@
       <c r="R433" s="1"/>
       <c r="S433" s="1"/>
       <c r="T433" s="1"/>
-      <c r="U433" s="1"/>
+      <c r="U433" s="20"/>
       <c r="V433" s="1"/>
       <c r="W433" s="1"/>
       <c r="X433" s="1"/>
@@ -36177,7 +36208,7 @@
       <c r="R434" s="1"/>
       <c r="S434" s="1"/>
       <c r="T434" s="1"/>
-      <c r="U434" s="1"/>
+      <c r="U434" s="20"/>
       <c r="V434" s="1"/>
       <c r="W434" s="1"/>
       <c r="X434" s="1"/>
@@ -36232,7 +36263,7 @@
       <c r="R435" s="1"/>
       <c r="S435" s="1"/>
       <c r="T435" s="1"/>
-      <c r="U435" s="1"/>
+      <c r="U435" s="20"/>
       <c r="V435" s="1"/>
       <c r="W435" s="1"/>
       <c r="X435" s="1"/>
@@ -36287,7 +36318,7 @@
       <c r="R436" s="1"/>
       <c r="S436" s="1"/>
       <c r="T436" s="1"/>
-      <c r="U436" s="1"/>
+      <c r="U436" s="20"/>
       <c r="V436" s="1"/>
       <c r="W436" s="1"/>
       <c r="X436" s="1"/>
@@ -36342,7 +36373,7 @@
       <c r="R437" s="1"/>
       <c r="S437" s="1"/>
       <c r="T437" s="1"/>
-      <c r="U437" s="1"/>
+      <c r="U437" s="20"/>
       <c r="V437" s="1"/>
       <c r="W437" s="1"/>
       <c r="X437" s="1"/>
@@ -36397,7 +36428,7 @@
       <c r="R438" s="1"/>
       <c r="S438" s="1"/>
       <c r="T438" s="1"/>
-      <c r="U438" s="1"/>
+      <c r="U438" s="20"/>
       <c r="V438" s="1"/>
       <c r="W438" s="1"/>
       <c r="X438" s="1"/>
@@ -36452,7 +36483,7 @@
       <c r="R439" s="1"/>
       <c r="S439" s="1"/>
       <c r="T439" s="1"/>
-      <c r="U439" s="1"/>
+      <c r="U439" s="20"/>
       <c r="V439" s="1"/>
       <c r="W439" s="1"/>
       <c r="X439" s="1"/>
@@ -36507,7 +36538,7 @@
       <c r="R440" s="1"/>
       <c r="S440" s="1"/>
       <c r="T440" s="1"/>
-      <c r="U440" s="1"/>
+      <c r="U440" s="20"/>
       <c r="V440" s="1"/>
       <c r="W440" s="1"/>
       <c r="X440" s="1"/>
@@ -36562,7 +36593,7 @@
       <c r="R441" s="1"/>
       <c r="S441" s="1"/>
       <c r="T441" s="1"/>
-      <c r="U441" s="1"/>
+      <c r="U441" s="20"/>
       <c r="V441" s="1"/>
       <c r="W441" s="1"/>
       <c r="X441" s="1"/>
@@ -36617,7 +36648,7 @@
       <c r="R442" s="1"/>
       <c r="S442" s="1"/>
       <c r="T442" s="1"/>
-      <c r="U442" s="1"/>
+      <c r="U442" s="20"/>
       <c r="V442" s="1"/>
       <c r="W442" s="1"/>
       <c r="X442" s="1"/>
@@ -36672,7 +36703,7 @@
       <c r="R443" s="1"/>
       <c r="S443" s="1"/>
       <c r="T443" s="1"/>
-      <c r="U443" s="1"/>
+      <c r="U443" s="20"/>
       <c r="V443" s="1"/>
       <c r="W443" s="1"/>
       <c r="X443" s="1"/>
@@ -36727,7 +36758,7 @@
       <c r="R444" s="1"/>
       <c r="S444" s="1"/>
       <c r="T444" s="1"/>
-      <c r="U444" s="1"/>
+      <c r="U444" s="20"/>
       <c r="V444" s="1"/>
       <c r="W444" s="1"/>
       <c r="X444" s="1"/>
@@ -36782,7 +36813,7 @@
       <c r="R445" s="1"/>
       <c r="S445" s="1"/>
       <c r="T445" s="1"/>
-      <c r="U445" s="1"/>
+      <c r="U445" s="20"/>
       <c r="V445" s="1"/>
       <c r="W445" s="1"/>
       <c r="X445" s="1"/>
@@ -36837,7 +36868,7 @@
       <c r="R446" s="1"/>
       <c r="S446" s="1"/>
       <c r="T446" s="1"/>
-      <c r="U446" s="1"/>
+      <c r="U446" s="20"/>
       <c r="V446" s="1"/>
       <c r="W446" s="1"/>
       <c r="X446" s="1"/>
@@ -36892,7 +36923,7 @@
       <c r="R447" s="1"/>
       <c r="S447" s="1"/>
       <c r="T447" s="1"/>
-      <c r="U447" s="1"/>
+      <c r="U447" s="20"/>
       <c r="V447" s="1"/>
       <c r="W447" s="1"/>
       <c r="X447" s="1"/>
@@ -36947,7 +36978,7 @@
       <c r="R448" s="1"/>
       <c r="S448" s="1"/>
       <c r="T448" s="1"/>
-      <c r="U448" s="1"/>
+      <c r="U448" s="20"/>
       <c r="V448" s="1"/>
       <c r="W448" s="1"/>
       <c r="X448" s="1"/>
@@ -37002,7 +37033,7 @@
       <c r="R449" s="1"/>
       <c r="S449" s="1"/>
       <c r="T449" s="1"/>
-      <c r="U449" s="1"/>
+      <c r="U449" s="20"/>
       <c r="V449" s="1"/>
       <c r="W449" s="1"/>
       <c r="X449" s="1"/>
@@ -37057,7 +37088,7 @@
       <c r="R450" s="1"/>
       <c r="S450" s="1"/>
       <c r="T450" s="1"/>
-      <c r="U450" s="1"/>
+      <c r="U450" s="20"/>
       <c r="V450" s="1"/>
       <c r="W450" s="1"/>
       <c r="X450" s="1"/>
@@ -37112,7 +37143,7 @@
       <c r="R451" s="1"/>
       <c r="S451" s="1"/>
       <c r="T451" s="1"/>
-      <c r="U451" s="1"/>
+      <c r="U451" s="20"/>
       <c r="V451" s="1"/>
       <c r="W451" s="1"/>
       <c r="X451" s="1"/>
@@ -37167,7 +37198,7 @@
       <c r="R452" s="1"/>
       <c r="S452" s="1"/>
       <c r="T452" s="1"/>
-      <c r="U452" s="1"/>
+      <c r="U452" s="20"/>
       <c r="V452" s="1"/>
       <c r="W452" s="1"/>
       <c r="X452" s="1"/>
@@ -37222,7 +37253,7 @@
       <c r="R453" s="1"/>
       <c r="S453" s="1"/>
       <c r="T453" s="1"/>
-      <c r="U453" s="1"/>
+      <c r="U453" s="20"/>
       <c r="V453" s="1"/>
       <c r="W453" s="1"/>
       <c r="X453" s="1"/>
@@ -37277,7 +37308,7 @@
       <c r="R454" s="1"/>
       <c r="S454" s="1"/>
       <c r="T454" s="1"/>
-      <c r="U454" s="1"/>
+      <c r="U454" s="20"/>
       <c r="V454" s="1"/>
       <c r="W454" s="1"/>
       <c r="X454" s="1"/>
@@ -37332,7 +37363,7 @@
       <c r="R455" s="1"/>
       <c r="S455" s="1"/>
       <c r="T455" s="1"/>
-      <c r="U455" s="1"/>
+      <c r="U455" s="20"/>
       <c r="V455" s="1"/>
       <c r="W455" s="1"/>
       <c r="X455" s="1"/>
@@ -37387,7 +37418,7 @@
       <c r="R456" s="1"/>
       <c r="S456" s="1"/>
       <c r="T456" s="1"/>
-      <c r="U456" s="1"/>
+      <c r="U456" s="20"/>
       <c r="V456" s="1"/>
       <c r="W456" s="1"/>
       <c r="X456" s="1"/>
@@ -37442,7 +37473,7 @@
       <c r="R457" s="1"/>
       <c r="S457" s="1"/>
       <c r="T457" s="1"/>
-      <c r="U457" s="1"/>
+      <c r="U457" s="20"/>
       <c r="V457" s="1"/>
       <c r="W457" s="1"/>
       <c r="X457" s="1"/>
@@ -37497,7 +37528,7 @@
       <c r="R458" s="1"/>
       <c r="S458" s="1"/>
       <c r="T458" s="1"/>
-      <c r="U458" s="1"/>
+      <c r="U458" s="20"/>
       <c r="V458" s="1"/>
       <c r="W458" s="1"/>
       <c r="X458" s="1"/>
@@ -37552,7 +37583,7 @@
       <c r="R459" s="1"/>
       <c r="S459" s="1"/>
       <c r="T459" s="1"/>
-      <c r="U459" s="1"/>
+      <c r="U459" s="20"/>
       <c r="V459" s="1"/>
       <c r="W459" s="1"/>
       <c r="X459" s="1"/>
@@ -37607,7 +37638,7 @@
       <c r="R460" s="1"/>
       <c r="S460" s="1"/>
       <c r="T460" s="1"/>
-      <c r="U460" s="1"/>
+      <c r="U460" s="20"/>
       <c r="V460" s="1"/>
       <c r="W460" s="1"/>
       <c r="X460" s="1"/>
@@ -37662,7 +37693,7 @@
       <c r="R461" s="1"/>
       <c r="S461" s="1"/>
       <c r="T461" s="1"/>
-      <c r="U461" s="1"/>
+      <c r="U461" s="20"/>
       <c r="V461" s="1"/>
       <c r="W461" s="1"/>
       <c r="X461" s="1"/>
@@ -37717,7 +37748,7 @@
       <c r="R462" s="1"/>
       <c r="S462" s="1"/>
       <c r="T462" s="1"/>
-      <c r="U462" s="1"/>
+      <c r="U462" s="20"/>
       <c r="V462" s="1"/>
       <c r="W462" s="1"/>
       <c r="X462" s="1"/>
@@ -37772,7 +37803,7 @@
       <c r="R463" s="1"/>
       <c r="S463" s="1"/>
       <c r="T463" s="1"/>
-      <c r="U463" s="1"/>
+      <c r="U463" s="20"/>
       <c r="V463" s="1"/>
       <c r="W463" s="1"/>
       <c r="X463" s="1"/>
@@ -37827,7 +37858,7 @@
       <c r="R464" s="1"/>
       <c r="S464" s="1"/>
       <c r="T464" s="1"/>
-      <c r="U464" s="1"/>
+      <c r="U464" s="20"/>
       <c r="V464" s="1"/>
       <c r="W464" s="1"/>
       <c r="X464" s="1"/>
@@ -37882,7 +37913,7 @@
       <c r="R465" s="1"/>
       <c r="S465" s="1"/>
       <c r="T465" s="1"/>
-      <c r="U465" s="1"/>
+      <c r="U465" s="20"/>
       <c r="V465" s="1"/>
       <c r="W465" s="1"/>
       <c r="X465" s="1"/>
@@ -37937,7 +37968,7 @@
       <c r="R466" s="1"/>
       <c r="S466" s="1"/>
       <c r="T466" s="1"/>
-      <c r="U466" s="1"/>
+      <c r="U466" s="20"/>
       <c r="V466" s="1"/>
       <c r="W466" s="1"/>
       <c r="X466" s="1"/>
@@ -37992,7 +38023,7 @@
       <c r="R467" s="1"/>
       <c r="S467" s="1"/>
       <c r="T467" s="1"/>
-      <c r="U467" s="1"/>
+      <c r="U467" s="20"/>
       <c r="V467" s="1"/>
       <c r="W467" s="1"/>
       <c r="X467" s="1"/>
@@ -38047,7 +38078,7 @@
       <c r="R468" s="1"/>
       <c r="S468" s="1"/>
       <c r="T468" s="1"/>
-      <c r="U468" s="1"/>
+      <c r="U468" s="20"/>
       <c r="V468" s="1"/>
       <c r="W468" s="1"/>
       <c r="X468" s="1"/>
@@ -38102,7 +38133,7 @@
       <c r="R469" s="1"/>
       <c r="S469" s="1"/>
       <c r="T469" s="1"/>
-      <c r="U469" s="1"/>
+      <c r="U469" s="20"/>
       <c r="V469" s="1"/>
       <c r="W469" s="1"/>
       <c r="X469" s="1"/>
@@ -38157,7 +38188,7 @@
       <c r="R470" s="1"/>
       <c r="S470" s="1"/>
       <c r="T470" s="1"/>
-      <c r="U470" s="1"/>
+      <c r="U470" s="20"/>
       <c r="V470" s="1"/>
       <c r="W470" s="1"/>
       <c r="X470" s="1"/>
@@ -38212,7 +38243,7 @@
       <c r="R471" s="1"/>
       <c r="S471" s="1"/>
       <c r="T471" s="1"/>
-      <c r="U471" s="1"/>
+      <c r="U471" s="20"/>
       <c r="V471" s="1"/>
       <c r="W471" s="1"/>
       <c r="X471" s="1"/>
@@ -38267,7 +38298,7 @@
       <c r="R472" s="1"/>
       <c r="S472" s="1"/>
       <c r="T472" s="1"/>
-      <c r="U472" s="1"/>
+      <c r="U472" s="20"/>
       <c r="V472" s="1"/>
       <c r="W472" s="1"/>
       <c r="X472" s="1"/>
@@ -38322,7 +38353,7 @@
       <c r="R473" s="1"/>
       <c r="S473" s="1"/>
       <c r="T473" s="1"/>
-      <c r="U473" s="1"/>
+      <c r="U473" s="20"/>
       <c r="V473" s="1"/>
       <c r="W473" s="1"/>
       <c r="X473" s="1"/>
@@ -38377,7 +38408,7 @@
       <c r="R474" s="1"/>
       <c r="S474" s="1"/>
       <c r="T474" s="1"/>
-      <c r="U474" s="1"/>
+      <c r="U474" s="20"/>
       <c r="V474" s="1"/>
       <c r="W474" s="1"/>
       <c r="X474" s="1"/>
@@ -38432,7 +38463,7 @@
       <c r="R475" s="1"/>
       <c r="S475" s="1"/>
       <c r="T475" s="1"/>
-      <c r="U475" s="1"/>
+      <c r="U475" s="20"/>
       <c r="V475" s="1"/>
       <c r="W475" s="1"/>
       <c r="X475" s="1"/>
@@ -38487,7 +38518,7 @@
       <c r="R476" s="1"/>
       <c r="S476" s="1"/>
       <c r="T476" s="1"/>
-      <c r="U476" s="1"/>
+      <c r="U476" s="20"/>
       <c r="V476" s="1"/>
       <c r="W476" s="1"/>
       <c r="X476" s="1"/>
@@ -38542,7 +38573,7 @@
       <c r="R477" s="1"/>
       <c r="S477" s="1"/>
       <c r="T477" s="1"/>
-      <c r="U477" s="1"/>
+      <c r="U477" s="20"/>
       <c r="V477" s="1"/>
       <c r="W477" s="1"/>
       <c r="X477" s="1"/>
@@ -38597,7 +38628,7 @@
       <c r="R478" s="1"/>
       <c r="S478" s="1"/>
       <c r="T478" s="1"/>
-      <c r="U478" s="1"/>
+      <c r="U478" s="20"/>
       <c r="V478" s="1"/>
       <c r="W478" s="1"/>
       <c r="X478" s="1"/>
@@ -38652,7 +38683,7 @@
       <c r="R479" s="1"/>
       <c r="S479" s="1"/>
       <c r="T479" s="1"/>
-      <c r="U479" s="1"/>
+      <c r="U479" s="20"/>
       <c r="V479" s="1"/>
       <c r="W479" s="1"/>
       <c r="X479" s="1"/>
@@ -38707,7 +38738,7 @@
       <c r="R480" s="1"/>
       <c r="S480" s="1"/>
       <c r="T480" s="1"/>
-      <c r="U480" s="1"/>
+      <c r="U480" s="20"/>
       <c r="V480" s="1"/>
       <c r="W480" s="1"/>
       <c r="X480" s="1"/>
@@ -38762,7 +38793,7 @@
       <c r="R481" s="1"/>
       <c r="S481" s="1"/>
       <c r="T481" s="1"/>
-      <c r="U481" s="1"/>
+      <c r="U481" s="20"/>
       <c r="V481" s="1"/>
       <c r="W481" s="1"/>
       <c r="X481" s="1"/>
@@ -38817,7 +38848,7 @@
       <c r="R482" s="1"/>
       <c r="S482" s="1"/>
       <c r="T482" s="1"/>
-      <c r="U482" s="1"/>
+      <c r="U482" s="20"/>
       <c r="V482" s="1"/>
       <c r="W482" s="1"/>
       <c r="X482" s="1"/>
@@ -38872,7 +38903,7 @@
       <c r="R483" s="1"/>
       <c r="S483" s="1"/>
       <c r="T483" s="1"/>
-      <c r="U483" s="1"/>
+      <c r="U483" s="20"/>
       <c r="V483" s="1"/>
       <c r="W483" s="1"/>
       <c r="X483" s="1"/>
@@ -38927,7 +38958,7 @@
       <c r="R484" s="1"/>
       <c r="S484" s="1"/>
       <c r="T484" s="1"/>
-      <c r="U484" s="1"/>
+      <c r="U484" s="20"/>
       <c r="V484" s="1"/>
       <c r="W484" s="1"/>
       <c r="X484" s="1"/>
@@ -38982,7 +39013,7 @@
       <c r="R485" s="1"/>
       <c r="S485" s="1"/>
       <c r="T485" s="1"/>
-      <c r="U485" s="1"/>
+      <c r="U485" s="20"/>
       <c r="V485" s="1"/>
       <c r="W485" s="1"/>
       <c r="X485" s="1"/>
@@ -39037,7 +39068,7 @@
       <c r="R486" s="1"/>
       <c r="S486" s="1"/>
       <c r="T486" s="1"/>
-      <c r="U486" s="1"/>
+      <c r="U486" s="20"/>
       <c r="V486" s="1"/>
       <c r="W486" s="1"/>
       <c r="X486" s="1"/>
@@ -39092,7 +39123,7 @@
       <c r="R487" s="1"/>
       <c r="S487" s="1"/>
       <c r="T487" s="1"/>
-      <c r="U487" s="1"/>
+      <c r="U487" s="20"/>
       <c r="V487" s="1"/>
       <c r="W487" s="1"/>
       <c r="X487" s="1"/>
@@ -39147,7 +39178,7 @@
       <c r="R488" s="1"/>
       <c r="S488" s="1"/>
       <c r="T488" s="1"/>
-      <c r="U488" s="1"/>
+      <c r="U488" s="20"/>
       <c r="V488" s="1"/>
       <c r="W488" s="1"/>
       <c r="X488" s="1"/>
@@ -39202,7 +39233,7 @@
       <c r="R489" s="1"/>
       <c r="S489" s="1"/>
       <c r="T489" s="1"/>
-      <c r="U489" s="1"/>
+      <c r="U489" s="20"/>
       <c r="V489" s="1"/>
       <c r="W489" s="1"/>
       <c r="X489" s="1"/>
@@ -39257,7 +39288,7 @@
       <c r="R490" s="1"/>
       <c r="S490" s="1"/>
       <c r="T490" s="1"/>
-      <c r="U490" s="1"/>
+      <c r="U490" s="20"/>
       <c r="V490" s="1"/>
       <c r="W490" s="1"/>
       <c r="X490" s="1"/>
